--- a/Avaliacao_Humano_Juiz.xlsx
+++ b/Avaliacao_Humano_Juiz.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arliene\Downloads\avaliacao\avaliacao\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C9F552-A922-4688-9ACC-2A7A0423B550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Avaliacao_Nery" sheetId="1" r:id="rId5"/>
+    <sheet name="Avaliacao_Nery" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="70">
   <si>
     <t>ID da Pergunta</t>
   </si>
@@ -68,9 +77,6 @@
 2.  Participar de grupos de apoio e partilha, onde você pode encontrar outras pessoas que vivem situações parecidas e trocar experiências.
 3.  Conversar com um psicólogo, que pode te ajudar a encontrar estratégias para lidar com o estresse e a sobrecarga.
 Você quer saber mais sobre: Sinais de esgotamento do cuidador, Como pedir ajuda ou A importância de cuidar de si mesmo? Basta me dizer qual assunto tem interesse.</t>
-  </si>
-  <si>
-    <t>"[\"Quando a pessoa com demência deixa de reconhecer a pessoa cuidadora e, por vezes, tem comportamentos agressivos ou desajustados, podemos ter a sensação de que a pessoa que conhecemos já não existe. Esta situação pode deixar-nos tristes e implicar o início de um processo de luto, ainda antes da pessoa falecer. Stresse e hipervigilância por ter de controlar constantemente situações de perigo. Quando a demência se agrava, pode ser necessário manter uma atenção constante aos comportamentos da pessoa – por exemplo, se ingere algo perigoso, se sai de casa sozinha e se perde, se liga o fogão e não desliga, se utiliza indevidamente algum objeto cortante. Esta situação pode ser física e emocionalmente desgastante, assim como limitar o descanso da pessoa cuidadora, aumentando o risco de exaustão. Exaustão, devido às dificuldades de comunicação. Podemos ter as mesmas conversas várias vezes ao dia com a pessoa ou repetir-nos exaustivamente para tentar dar orientações, mas, devido às dificuldades em reter informação, a comunicação fica comprometida. Estas repetições constantes, apesar de fazerem parte do quadro da doença, podem causar muito cansaço emocional. Frustração, por não conseguir acalmar a pessoa. Em momentos de maior agitação e confusão (por exemplo, quando a pessoa não nos reconhece e quer fugir de casa), os esforços que fazemos para chamar a pessoa à razão parecem não resultar e podem deixar-nos frustrados/as. Podemos acabar por tomar medidas com as quais nem concordamos, mas que nos parecem a única solução para manter a pessoa em segurança (por exemplo, trancar as portas e as janelas). Zanga, perante certos comportamentos. Quando a pessoa com demência tem comportamentos que parecem complicar mais a situação (por exemplo, entornar comida, cortar cabos, passar a noite acordado/a, tentar fugir de casa), podemos sentir-nos zangados/as e impotentes, mesmo sabendo que a pessoa não pode ser responsabilizada. ”Presos/as” ao papel de cuidador ou cuidadora. Com o agravar da doença, a pessoa cuidada fica cada vez mais dependente e podemos ser forçados/as a deixar de trabalhar ou a abandonar outras atividades e relações, sentindo também uma perda da nossa identidade anterior para além do papel de pessoa cuidadora. Por outro lado, as cuidadoras e os cuidadores informais de pessoas com demência podem sentir satisfação por desempenharem um papel importante na vida da pessoa cuidada. Também podemos sentir que estamos a retribuir o cuidado que a pessoa nos deu anteriormente ou sentir gratificação por, apesar da doença, vermos a pessoa tranquila e feliz. Cuidar de alguém que vai se esquecendo de quem é pode mudar a maneira como vemos o mundo. Podemos começar a dar maior importância à Saúde e a momentos que vivemos com familiares e amigos e amigas. Podemos sentir-nos mais resilientes e sentir maior compaixão para com outras pessoas que vivem situações semelhantes. | 32 ANIGÁP | SIAMROFNI SERODADIUC SOD ODADIUCOTUA ERBOS RALAF SOMAV ENQUANTO CUIDADORES E CUIDADORAS, É IMPORTANTE LEMBRARMO-NOS QUE: Um psicólogo ou uma psicóloga pode ajudar-nos a descobrir e a treinar estratégias para acalmar a pessoa quando esta está agitada e confusa. Podemos participar em grupos de apoio e partilha (por exemplo, o Café Memória) onde podemos encontrar apoio emocional e trocar experiências com pessoas que vivem situações semelhantes à nossa. A ajuda de familiares, amigos, amigas, vizinhos e vizinhas e profissionais (assistentes pessoais) pode assegurar alguma autonomia à pessoa cuidada, evitar a nossa sobrecarga e permitirnos ter mais tempo para nós. PORQUE É IMPORTANTE CUIDAR DE MIM? 0 3 VOLTAR AO ÍNDICE Cuidar de nós é fundamental para conseguirmos cuidar de alguém que precisa do nosso apoio. Cuidar de nós significa mantermos a capacidade e a disponibilidade, física e emocional, que são necessárias para cuidarmos de outra pessoa.\",\"Descanse Para que mantenha a sua própria saúde, tanto psicológica como física equilibrada, é necessário que descanse da tarefa de cuidar de forma regular. Alimente-se adequadamente Para que se sinta com mais energia deve fazer uma dieta equilibrada e diversificada. Pratique exercício Ajuda a reduzir o stress, previne doenças cardiovasculares, ajuda a dormir melhor e previne a osteoporose. Manual do Cuidador Informal Página 5 4 - GESTÃO DO STRESS Solicite e aceite ajuda Assegure-se que tem metas e expectativas realistas. Não espere ter uma casa perfeita ou uma vida social como a que tinha antes de assumir o papel como prestador de cuidados. O humor é por vezes o melhor remédio. O humor pode realizar milagres como meio de reduzir o stress. Procure apoios através de amigos, grupos de apoio ou um profissional. Evite pessoas difíceis, com por exemplo amigos que criticam demasiado. 4.1 - POSSÍVEIS SINAIS DE ESGOTAMENTO E/OU STRESS  Problemas de sono;  Perca de energia, fadiga crónica, sensação de cansaço contínuo;  Isolamento;  Consumo excessivo de bebidas com cafeína, álcool, tabaco e medicamentos;  Problemas de memória e concentração;  Menor interesse pelas actividades e pessoas que anteriormente eram objecto de interesse;  Aumento ou diminuição do apetite;  Dar demasiada importância a pequenos detalhes;  Mudanças frequentes de humor ou do estado de ânimo. Se apresenta alguns destes sintomas, poderá estar a carregar um peso demasiado elevado.\",\"Raiva: diante das sua recusas, falta de controle dos esfíncteres. ! Ansiedade: por espera de progresso do paciente, para sair da rotina do dia a dia da doença. ! Culpa: por ter pensamento e atitudes as vezes negativas. Pode vivenciar: ! Cansaço. ! Insônia. ! Perda de autocontrole. ! Impotência. ! Depressão. Calma! Procure: ! Deixar o idoso sempre ocupado. ! Assistir à TV. 71 Manual para Cuidadores Informais de Idosos ! Se possível caminhar, tomar banho de sol e fazer alguns exercícios dentro de seus limites. ! Incentivá-lo a rezar (se o paciente for religioso). ! Não responder pelo paciente. ! Não faça por ele o que ele pode fazer. ! Sair de perto quando estiver perdendo o autocontrole e solicitar ajuda de outro cuidador da família ou voluntário. ! Sempre que possível revezar com alguém. ! Procurar se informar a respeito da evolução da patologia. ! Procurar recursos existentes na comunidade. ! Procurar recursos oferecidos pela saúde como: grupos existentes nos centros de saúde (Lian-Gong, Caminhada, Ginástica etc...) ! Conversar com familiares que também tenham seus doentes. ! Tente manter as atividades possíveis que o paciente executava como: dobrar roupas, vestir-se e etc. ! Cuidado com seus gestos ou palavras, o paciente é atento. ! Revezar entre os membros da família e amigos horário com disponibilidade interna de conversar/dialogar com carinho e ternura com o paciente. !\",\"Esses ao que podemos fazer para que ela tenha uma boa desafios podem exigir diferentes tipos de cuida- qualidade vida. dos. Para garantir a participação plena da criança no jardim de infância, na escola e noutros contextos Quando cuidadoras ou cuidadores informais são os é fundamental que esses ambientes estejam pre- pais, mães, cuidar pode significar assumir um papel parados, com os devidos recursos, acessibilidade e mais exigente e durante mais tempo do que esperaestratégias de inclusão, o que pode também implicar vam – nalguns casos, a necessidade de apoio diário uma preparação mais aprofundada por parte das pode estender-se por toda a vida. cuidadoras ou dos cuidadores informais. | 61 ANIGÁP | SIAMROFNI SERODADIUC SOD ODADIUCOTUA ERBOS RALAF SOMAV AS CUIDADORAS OU CUIDADORES INFORMAIS DE UMA CRIANÇA COM DEFICIÊNCIA PODEM SENTIR: Dificuldade em aceitar a situação. O confronto com o diagnóstico de deficiência de uma criança pode gerar choque, descrença no que está a acontecer, revolta, zanga quer com o profissional de saúde que nos deu a notícia, com o nosso parceiro ou parceira a ou até connosco. Por vezes, podemos sentir que ignoramos a criança e oscilar entre sentimentos de indiferença, rejeição e culpa. Estes sentimentos são comuns, difíceis de gerir e podem afetar a nossa relação com a criança. Por isso, é importante procurar apoio – um Psicólogo ou Psicóloga pode ajudar. Necessidade de fazer o luto por uma criança que se imaginou. É natural que, antes e durante a gravidez, os pais e mães desejem uma criança saudável e que até a imaginem com determinadas características. Quando percebemos que a criança é diferente daquilo que imaginámos, é comum sentirmo-nos tristes, impotentes, envergonhados, envergonhadas e, ou desiludidos, desiludidas. É importante permitir-nos sentir essas emoções e aprender a adaptar-nos a uma “criança real” que é diferente daquela que imaginámos, valorizando as suas particularidades e o seu potencial. Ansiedade e preocupação com o futuro da criança. É natural questionarmo-nos sobre se a criança poderá ter uma vida autónoma e feliz, fazer algo de que goste e manter relações significativas. Podemos ainda ter receio de que, se algo nos acontecer, a criança perca as pessoas que melhor a conhecem e mais a ajudam, ficando sem apoio. Stresse e dificuldades noutras áreas da vida. Com as aprendizagens e tarefas que se associam ao cuidar de uma criança com deficiência, podemos sentir-nos stressados e irritáveis, podendo ficar menos produtivas no trabalho ou investir menos na relação com o nosso parceiro ou parceira, outros filhos ou filhas, familiares e amigos ou amigas. Frustração com a falta de conhecimento sobre a deficiência. Além da exigência dos cuidados, podemos ter de lidar com pessoas que fazem comentários desadequados ou limitam a sua interação com a criança, em função de crenças desadequadas e falta de informação sobre a deficiência. Por exemplo, na escola, certos profissionais podem não saber lidar com as características da criança e adotar comportamentos que não ajudam a criança ou que dificultam a sua aprendizagem e inclusão. Estas situações podem levar-nos a sentir que estamos sozinhos/as ou em constante confronto com os outros – como o sentimento de que “somos nós contra o mundo”. Por outro lado, enquanto pessoa cuidadora de crianças com deficiência também podemos descobrir forças que não sabíamos que tínhamos. Com o passar do tempo e e com a experiência, podemos sentir mais confiança na ...</t>
   </si>
   <si>
     <t>P1-06</t>
@@ -131,9 +137,6 @@
 Infelizmente, não tenho essa informação nos meus manuais no momento, mas meu conhecimento está sendo aprimorado constantemente. Sugiro que anote essa dúvida para conversar com um profissional de saúde ou diretamente com a operadora do plano de saúde.</t>
   </si>
   <si>
-    <t>"[\"A classificação da complexidade assistencial em AD tem por finalidade: a. Admissão no SAD, aliada aos critérios de inclusão nas modalidades de Atenção Domiciliar; b. Migração da modalidade assistencial, conforme evolução clínica do usuário; c. Apoio na elaboração do plano terapêutico, sugerindo periodicidade de visitas dos profissionais das equipes de Saúde, insumos, logística de transporte e agendamentos necessários. Os itens “a” e “b”, que se referem aos critérios de admissão no SAD, determinação da modalidade de AD e migração entre modalidades, auxiliam na organização dos SADs e dizem respeito, em grande medida, aos critérios que delimitam as modalidades de Atenção Domiciliar. Dessa forma, é importante ressaltar que a classificação da complexidade do paciente é, com o preparo do domicílio e a articulação da família/cuidador, a primeira etapa para a realização do cuidado em AD, na medida em que determina a equipe que se responsabilizará pelo cuidado de forma mais protagonista (equipe de Atenção Básica ou Emad), o número mínimo de visitas mensais e o plano terapêutico, projetos terapêuticos singulares (PTS), no caso de pacientes complexos – ver Capítulo 1. Na análise da literatura existente sobre métodos para classificar pacientes em Atenção Domiciliar utilizados em outros países e em experiências brasileiras, há várias referências bibliográficas. Analisando escalas e instrumentos de avaliação que vêm sendo aplicados nos serviços de Atenção Domiciliar públicos e privados no Brasil, podemos subdividi-los em categorias que são mais significativas para a prática dos serviços, como os aspectos clínicos, socioeconômicos e ambientais. A partir do diagnóstico em saúde, que antecede o planejamento da AD, os serviços locais podem selecionar quais aspectos seriam mais importantes para definir uma classificação da complexidade, de acordo com os indicadores de Saúde e de organização de serviço em cada localidade. Assim, de forma esquemática, nos aspectos clínicos, estariam contempladas as seguintes variáveis, que deverão ser consideradas em conjunto para a elegibilidade do usuário em AD: a) Utilização de serviços de Saúde: número e tempo de permanência de internações no último ano (hospitalizações) e atendimentos nos serviços de urgência/emergência; b) Quadro clínico: acamado, sequelado, presença de doenças agudas e crônicas, com estabilidade clínica, passíveis de tratamento em domicílio; distúrbio do nível de consciência; estabilidade hemodinâmica; padrão respiratório; comprometimento do estado nutricional; 37 Ministério da Saúde c) Suporte terapêutico: – Terapia medicamentosa: medicação prescrita e vias de administração; – Suporte respiratório; dependência de oxigenoterapia; presença de hipersecreção pulmonar; necessidade de aspirações orotraqueais; ventilação mecânica não invasiva; – Terapia nutricional: suplementação oral ou enteral; d)Reabilitação: incapacidade funcional para atividades da vida diária (AVDs) e atividades da vida diária instrumentais (AVDIs); plegias; distúrbios fonoaudiológicos; necessidade de cuidados de reabilitação fisioterápica; adaptação de órteses e próteses em AD; e)Uso de drenos, cateteres e estomias; f)Cuidados de enfermagem: presença de feridas; necessidade de administração de medicamentos via parenteral; monitoramento de sinais vitais; g)Realização de exames complementares; h)Cuidados paliativos. Nos aspectos socioeconômicos e ambientais, serão consideradas, em conjunto, as seguintes variáveis: a)Risco social familiar: drogadição, desemprego, analfabetismo; b)Presença de cuidador e necessidade de treinamento/capacitação; c)Estrutura familiar; consentimento e participação familiar; idoso sozinho e rede social de apoio; d)Condições de moradia; relação morador/cômodo; saneamento básico; e)Segurança dos profissionais da equipe; acessibilidade ao domicílio.\",\"Porém, se houver alto uso de tecnologias e necessidade de visitas multiprofissionais mais frequentes, estão indicadas as modalidades AD2 e AD3 pelas Emads. Estes pacientes são os grandes incapacitados, com sequelas de doenças crônicas incapacitantes, entre elas, as neurodegenerativas. São mais importantes os processos de cuidado, a instrumentalização da família e o olhar da longitudinalidade, que auxiliará no fortalecimento de vínculos e de confiança, fundamentais para o processo de cuidados compartilhados. No Brasil, já existe a necessidade urgente de efetivação do processo de intersetorialidade entre o Sistema Único da Assistência Social (Suas) e o SUS, como já ocorre em outros países com tradição nos cuidados de longa duração, sejam eles na comunidade ou institucionais, pois o envelhecimento populacional demandará outros arranjos na organização dos cuidados domiciliares, e nem sempre a equipe de Saúde poderá dar conta de todas as demandas de cuidados nos lares – este tema poderá ganhar destaque em futuras edições deste material escrito. Os cuidados paliativos (CPs) domiciliares podem se enquadrar tanto nas modalidades de curta, média ou longa permanências, a depender das características do paciente e de suas comorbidades, além do estado funcional quando é encaminhado para a AD. É preferível que os pacientes de CP sejam encaminhados em uma fase anterior aos últimos dias ou semanas de vida, para que haja possibilidade de se criar vínculos em uma fase tão aflitiva que é o final da vida. Não é obrigatório que o paciente fique estanque em um patamar rígido de modalidade assistencial de AD. Se ocorrer a melhora funcional, deve-se evitar a alta sumária do programa, com o correto encaminhamento e a garantia de acesso a outros pontos de atenção da rede. Pode e deve transitar entre os vários níveis de complexidade de AD, como no exemplo abaixo: Dona S., 64 anos, recebeu alta hospitalar após duas semanas internada na enfermaria de clínica médica por acidente vascular cerebral isquêmico (AVCI) de artéria cerebral média D, com diagnóstico recente também de flutter atrial e insuficiência cardíaca congestiva (ICC). No início, foram frequentes as visitas com controle de coagulograma e ajuste mais fino de drogas para ICC e antiarrítmicos, além das várias orientações aos cuidadores e paciente após AVCI. Após seis semanas, em anticoagulação oral estabilizada, aumentou-se o intervalo das visitas de duas para quatro semanas, e a família encontrava-se mais tranquila e segura com os cuidados. Quatro meses depois, foi encaminhada para o centro de reabilitação ambulatorial – não tinha condição de marcha funcional autônoma e havia o risco de quedas com sangramento maciço, caso sofresse lesão corporal. Nesse centro de reabilitação, não havia a possibilidade de controle ambulatorial de tempo de protrombina – a família tinha que levá-la todo mês ao laboratório do hospital que havia encaminhado a paciente à AD e, no momento do encaminhamento à reabilitação, voltou a ser acompanhada pela Atenção Básica e pelo ambulatório de especialidade em Cardiologia, com período de observação da equipe de AD para observar se a transição ocorreria de forma tranquila. No mesmo ano, em pleno inverno, no segundo mês após iniciar a reabilitação, iniciou quadro de piora da dispneia e febrícula, e sua filha acionou a equipe de Atenção Básica (AB). Em visita domiciliar, diagnosticou-se broncopneumonia e novamente a equipe de AD foi acionada (agora pela AB), que passou novamente a realizar visitas que se aproximaram com intervalo semanal, quinzenal e depois mensal, pela intercorrência aguda instalada.\",\"96p. : il. Modo de acesso: World Wide Web: &lt;http://bvsms.saude.gov.br/bvs/publicacoes/orientacoes_cuidado_paciente_ambiente_domiciliar.pdf&gt; ISBN 978-85-334-2598-9 1. Cuidador. 2. Atenção domiciliar. 3. Serviços de saúde. I. Título. II. Hospital Alemão Oswaldo Cruz. CDU 616-08:364-783 _______________________________________________________________________________________________ Catalogação na fonte – Coordenação-Geral de Documentação e Informação – Editora MS – OS 2017/0120 Títulos para indexação: Orientations for home health care SUMÁRIO Contatos úteis ..................................................................................................05 Informações gerais ..........................................................................................07 Cuidador............................................................................................................11 Cuide-se para poder cuidar ................................................................................11 Cuidando do paciente.......................................................................................13 Higiene pessoal ..................................................................................................13 Cuidado com os medicamentos ..........................................................................15 Pessoa com convulsão ........................................................................................17 Lavagem das mãos ..............................................................................................19 Segurança do paciente na atenção domiciliar .....................................................23 Cuidados com o lixo infectante ..........................................................................28 Equipamentos de proteção individual .................................................................29 Cânula de traqueostomia ...............................................................................31 Aspiração .........................................................................................................37 Cuidados com a ventilação mecânica não invasiva - CPAP ou BIPAP ..........43 Lesão por pressão ............................................................................................49 Orientações para exercícios básicos ...............................................................55 Sonda enteral ...................................................................................................59 Gastrostomia e jejunostomia .........................................................................71 Sondagem vesical e cistostomia ....................................................................75 Cuidados com acesso venoso ...............................</t>
-  </si>
-  <si>
     <t>P2-14</t>
   </si>
   <si>
@@ -148,9 +151,6 @@
 4.  **Busque apoio profissional:** Um psicólogo pode ajudar a encontrar e treinar estratégias para acalmar a pessoa quando ela estiver muito agitada ou confusa.
 5.  **Cuide de você também:** Se a pessoa estiver perdendo o controle e você sentir que está perdendo o seu, tente se afastar um pouco e pedir ajuda a outro cuidador da família ou a um voluntário, se for possível.
 Você quer saber mais sobre: Como posso promover a autonomia do paciente, Onde posso encontrar grupos de apoio para cuidadores ou Como lidar com a minha própria frustração? Basta me dizer qual assunto tem interesse.</t>
-  </si>
-  <si>
-    <t>"[\"Quando a pessoa com demência deixa de reconhecer a pessoa cuidadora e, por vezes, tem comportamentos agressivos ou desajustados, podemos ter a sensação de que a pessoa que conhecemos já não existe. Esta situação pode deixar-nos tristes e implicar o início de um processo de luto, ainda antes da pessoa falecer. Stresse e hipervigilância por ter de controlar constantemente situações de perigo. Quando a demência se agrava, pode ser necessário manter uma atenção constante aos comportamentos da pessoa – por exemplo, se ingere algo perigoso, se sai de casa sozinha e se perde, se liga o fogão e não desliga, se utiliza indevidamente algum objeto cortante. Esta situação pode ser física e emocionalmente desgastante, assim como limitar o descanso da pessoa cuidadora, aumentando o risco de exaustão. Exaustão, devido às dificuldades de comunicação. Podemos ter as mesmas conversas várias vezes ao dia com a pessoa ou repetir-nos exaustivamente para tentar dar orientações, mas, devido às dificuldades em reter informação, a comunicação fica comprometida. Estas repetições constantes, apesar de fazerem parte do quadro da doença, podem causar muito cansaço emocional. Frustração, por não conseguir acalmar a pessoa. Em momentos de maior agitação e confusão (por exemplo, quando a pessoa não nos reconhece e quer fugir de casa), os esforços que fazemos para chamar a pessoa à razão parecem não resultar e podem deixar-nos frustrados/as. Podemos acabar por tomar medidas com as quais nem concordamos, mas que nos parecem a única solução para manter a pessoa em segurança (por exemplo, trancar as portas e as janelas). Zanga, perante certos comportamentos. Quando a pessoa com demência tem comportamentos que parecem complicar mais a situação (por exemplo, entornar comida, cortar cabos, passar a noite acordado/a, tentar fugir de casa), podemos sentir-nos zangados/as e impotentes, mesmo sabendo que a pessoa não pode ser responsabilizada. ”Presos/as” ao papel de cuidador ou cuidadora. Com o agravar da doença, a pessoa cuidada fica cada vez mais dependente e podemos ser forçados/as a deixar de trabalhar ou a abandonar outras atividades e relações, sentindo também uma perda da nossa identidade anterior para além do papel de pessoa cuidadora. Por outro lado, as cuidadoras e os cuidadores informais de pessoas com demência podem sentir satisfação por desempenharem um papel importante na vida da pessoa cuidada. Também podemos sentir que estamos a retribuir o cuidado que a pessoa nos deu anteriormente ou sentir gratificação por, apesar da doença, vermos a pessoa tranquila e feliz. Cuidar de alguém que vai se esquecendo de quem é pode mudar a maneira como vemos o mundo. Podemos começar a dar maior importância à Saúde e a momentos que vivemos com familiares e amigos e amigas. Podemos sentir-nos mais resilientes e sentir maior compaixão para com outras pessoas que vivem situações semelhantes. | 32 ANIGÁP | SIAMROFNI SERODADIUC SOD ODADIUCOTUA ERBOS RALAF SOMAV ENQUANTO CUIDADORES E CUIDADORAS, É IMPORTANTE LEMBRARMO-NOS QUE: Um psicólogo ou uma psicóloga pode ajudar-nos a descobrir e a treinar estratégias para acalmar a pessoa quando esta está agitada e confusa. Podemos participar em grupos de apoio e partilha (por exemplo, o Café Memória) onde podemos encontrar apoio emocional e trocar experiências com pessoas que vivem situações semelhantes à nossa. A ajuda de familiares, amigos, amigas, vizinhos e vizinhas e profissionais (assistentes pessoais) pode assegurar alguma autonomia à pessoa cuidada, evitar a nossa sobrecarga e permitirnos ter mais tempo para nós. PORQUE É IMPORTANTE CUIDAR DE MIM? 0 3 VOLTAR AO ÍNDICE Cuidar de nós é fundamental para conseguirmos cuidar de alguém que precisa do nosso apoio. Cuidar de nós significa mantermos a capacidade e a disponibilidade, física e emocional, que são necessárias para cuidarmos de outra pessoa.\",\"Raiva: diante das sua recusas, falta de controle dos esfíncteres. ! Ansiedade: por espera de progresso do paciente, para sair da rotina do dia a dia da doença. ! Culpa: por ter pensamento e atitudes as vezes negativas. Pode vivenciar: ! Cansaço. ! Insônia. ! Perda de autocontrole. ! Impotência. ! Depressão. Calma! Procure: ! Deixar o idoso sempre ocupado. ! Assistir à TV. 71 Manual para Cuidadores Informais de Idosos ! Se possível caminhar, tomar banho de sol e fazer alguns exercícios dentro de seus limites. ! Incentivá-lo a rezar (se o paciente for religioso). ! Não responder pelo paciente. ! Não faça por ele o que ele pode fazer. ! Sair de perto quando estiver perdendo o autocontrole e solicitar ajuda de outro cuidador da família ou voluntário. ! Sempre que possível revezar com alguém. ! Procurar se informar a respeito da evolução da patologia. ! Procurar recursos existentes na comunidade. ! Procurar recursos oferecidos pela saúde como: grupos existentes nos centros de saúde (Lian-Gong, Caminhada, Ginástica etc...) ! Conversar com familiares que também tenham seus doentes. ! Tente manter as atividades possíveis que o paciente executava como: dobrar roupas, vestir-se e etc. ! Cuidado com seus gestos ou palavras, o paciente é atento. ! Revezar entre os membros da família e amigos horário com disponibilidade interna de conversar/dialogar com carinho e ternura com o paciente. !\",\"Esses ao que podemos fazer para que ela tenha uma boa desafios podem exigir diferentes tipos de cuida- qualidade vida. dos. Para garantir a participação plena da criança no jardim de infância, na escola e noutros contextos Quando cuidadoras ou cuidadores informais são os é fundamental que esses ambientes estejam pre- pais, mães, cuidar pode significar assumir um papel parados, com os devidos recursos, acessibilidade e mais exigente e durante mais tempo do que esperaestratégias de inclusão, o que pode também implicar vam – nalguns casos, a necessidade de apoio diário uma preparação mais aprofundada por parte das pode estender-se por toda a vida. cuidadoras ou dos cuidadores informais. | 61 ANIGÁP | SIAMROFNI SERODADIUC SOD ODADIUCOTUA ERBOS RALAF SOMAV AS CUIDADORAS OU CUIDADORES INFORMAIS DE UMA CRIANÇA COM DEFICIÊNCIA PODEM SENTIR: Dificuldade em aceitar a situação. O confronto com o diagnóstico de deficiência de uma criança pode gerar choque, descrença no que está a acontecer, revolta, zanga quer com o profissional de saúde que nos deu a notícia, com o nosso parceiro ou parceira a ou até connosco. Por vezes, podemos sentir que ignoramos a criança e oscilar entre sentimentos de indiferença, rejeição e culpa. Estes sentimentos são comuns, difíceis de gerir e podem afetar a nossa relação com a criança. Por isso, é importante procurar apoio – um Psicólogo ou Psicóloga pode ajudar. Necessidade de fazer o luto por uma criança que se imaginou. É natural que, antes e durante a gravidez, os pais e mães desejem uma criança saudável e que até a imaginem com determinadas características. Quando percebemos que a criança é diferente daquilo que imaginámos, é comum sentirmo-nos tristes, impotentes, envergonhados, envergonhadas e, ou desiludidos, desiludidas. É importante permitir-nos sentir essas emoções e aprender a adaptar-nos a uma “criança real” que é diferente daquela que imaginámos, valorizando as suas particularidades e o seu potencial. Ansiedade e preocupação com o futuro da criança. É natural questionarmo-nos sobre se a criança poderá ter uma vida autónoma e feliz, fazer algo de que goste e manter relações significativas. Podemos ainda ter receio de que, se algo nos acontecer, a criança perca as pessoas que melhor a conhecem e mais a ajudam, ficando sem apoio. Stresse e dificuldades noutras áreas da vida. Com as aprendizagens e tarefas que se associam ao cuidar de uma criança com deficiência, podemos sentir-nos stressados e irritáveis, podendo ficar menos produtivas no trabalho ou investir menos na relação com o nosso parceiro ou parceira, outros filhos ou filhas, familiares e amigos ou amigas. Frustração com a falta de conhecimento sobre a deficiência. Além da exigência dos cuidados, podemos ter de lidar com pessoas que fazem comentários desadequados ou limitam a sua interação com a criança, em função de crenças desadequadas e falta de informação sobre a deficiência. Por exemplo, na escola, certos profissionais podem não saber lidar com as características da criança e adotar comportamentos que não ajudam a criança ou que dificultam a sua aprendizagem e inclusão. Estas situações podem levar-nos a sentir que estamos sozinhos/as ou em constante confronto com os outros – como o sentimento de que “somos nós contra o mundo”. Por outro lado, enquanto pessoa cuidadora de crianças com deficiência também podemos descobrir forças que não sabíamos que tínhamos. Com o passar do tempo e e com a experiência, podemos sentir mais confiança na nossa capacidade de lidar com situações desafiantes. Podemos olhar para as outras pessoascom mais sensibilidade e compaixão e até descobrir potencialidades onde outras pessoas não as veem. Cuidar de uma criança com deficiência também inclui momentos felizes. Assistir ao seu desenvolvimento - seja quando aprende a comunicar, conquista autonomia numa tarefa, desenvolve os seus interesses ou partilha momentos de brincadeira com os seus amigos), pode gerar sentimentos de orgulhoso, gratidão e esperança.\",\"Às vezes, podemos também sentir que o nosso parceiro ou a nossa parceira nos deixa com a maior parte das responsabilidade e tarefas de cuidado. Podemos acabar por nos sentir sozinhos ou sozinhas, atarefados ou atarefadas e sem tempo, priorizando sempre a responsabilidade de cuidar da pessoa. | 72 ANIGÁP | SIAMROFNI SERODADIUC SOD ODADIUCOTUA ERBOS RALAF SOMAV Algumas barreiras ao autocuidado podem ser ultrapassadas. Outras, podem ser difíceis de ultrapassar, porque não dependem apenas de nós. No entanto, há algumas soluções que podemos tentar: • Explorar a possibilidade de obter apoios sociais. Existem alguns apoios sociais que são destinados a cuidadores e cuidadoras informais e a pessoas que se encontram em situação de dependência. O Estatuto do Cuidador Informal concede alguns apoios, não só financeiros, mas também no acesso a uma maior rede de apoio. Também existem apoios da Segurança Social que se destinam a pessoas cuidadas. • Ir além de uma atitu...</t>
   </si>
   <si>
     <t>P2-17</t>
@@ -201,9 +201,6 @@
 Você quer saber mais sobre: Como administrar medicamentos se o idoso tem dificuldade para engolir, O que é espessante alimentar ou Qual a diferença entre medicamento de referência e genérico? Basta me dizer qual assunto tem interesse.</t>
   </si>
   <si>
-    <t>"[\"6 Pacientes com limitação de ingesta hídrica devem seguir as orientações do prescritor da medicação. Uma medicação só deve ser tomada com leite se houver recomendação médica, pois muitos medicamentos interagem com o cálcio do leite, interferindo no efeito desejado do medicamento. 6 Em caso de dificuldade de deglutição e o paciente se alimentar com restrições de consistência, utilizar como auxílio para a administração dos medicamentos o espessante alimentar na água. CAPÍTULO 10 10. O que é espessante alimentar? Espessante alimentar são produtos industrializados que modificam instantaneamente a textura e consistência dos alimentos. Ele é uma substância sem sabor capaz de aumentar a viscosidade dos alimentos que estão na forma líquida. 7,13 CAPÍTULO 11 11. É importante informar aos profissionais de saúde quais os medicamentos e como o idoso faz uso A reconciliação de medicamentosa é a obtenção de uma lista completa, precisa e atualizada dos medicamentos que o paciente utiliza em casa (incluindo nome, dosagem, frequência e via de administração), e comparada com as prescrições médicas feitas na admissão, transferência, consultas ambulatoriais com outros médicos e durante a alta hospitalar, visando assegurar a terapêutica de um tratamento individualizado. 1 LEVAR NOS ATENDIMENTOS AS RECEITAS ORIGINAIS OU CÓPIAS, E/OU AINDA, LEVAR UMA SACOLINHA COM AS CAIXINHAS QUE O PACIENTE USA. CAPÍTULO 12 12. O que é medicamento de referência? O medicamento de referência, também chamados “de marca”, são os medicamentos com novos princípios ativos ou que são novidades no tratamento de doenças. Possuem o registro de inovador, cuja eficácia, segurança e qualidade foram comprovadas cientificamente perante o Órgão Federal competente. 2 A indústria farmacêutica que investiu anos em pesquisa, por um período de tempo, garante direitos exclusivos de exploração (produção, utilização e comercialização sem concorrência) do medicamento. Após a expiração dessa patente, há a liberação para produção de medicamentos genéricos e similares. 2 CAPÍTULO 13 13. O que é medicamento genérico? Medicamentos Genéricos - são medicamentos produzi- MEDICAMENTO DE REFERÊNCIA X MEDICAMENTO GENÉRICO dos após a expiração da proteção da patente ou de outros direitos de exclusividade. São realizados testes de bioequivalência e equivalência farmacêutica, comprovando sua eficácia, segurança e qualidade, igual a do medicamento de referência ou inovador. Os medicamentos genéricos agem em nosso organismo da mesma forma que os medicamentos de referência agiriam. 2 Na embalagem do remédio genérico há uma tarja amarela, contendo a letra “G”, com os dizeres “Medicamento Genérico”. Esse tipo de medicamento não tem marca, o nome do produto será sempre um princípio ativo. 2 CAPÍTULO 14 14. O que é medicamento similar equivalente? Os medicamentos similares equivalentes são identificados pela marca ou nome comercial. Possuem o mesmo princípio ativo, na mesma forma farmacêutica e via de administração dos medicamentos de referência e também são aprovados nos testes de qualidade da ANVISA. A diferença entre os similares e os de referência está relacionada a alguns aspectos como: prazo de validade do medicamento, embalagem, rotulagem, no tamanho e formato do produto. 2 MEDICAMENTO DE REFERÊNCIA X MEDICAMENTO GENÉRICO X MEDICAMENTO SIMILAR EQUIVALENTE UM EXEMPLO É A ASPIRINA (REFERÊNCIA), ÁCIDO ACETILSALICÍLICO (GENÉRICO) E O MELHORAL (SIMILAR). CAPÍTULO 15 15. Qual a diferença de nome comercial e princípio ativo? O nome comercial é o nome fantasia criado pela indústria e princípio ativo é o nome da substância química composta no medicamento. Identificar esses itens na caixa de medicamento reduz os casos de duplicidade de droga. Lembrete: Importante sempre estar verificando o prazo de validade dos medicamentos, durante o momento da compra ou da aquisição e nos momentos das tomadas. CAPÍTULO 16 16.\",\"45 Manual para Cuidadores Informais de Idosos DIETA PARA DIARRÉIA ORIENTAÇÕES: ! Aumentar a ingestão de líquidos e soluções glicofisiológicas (soro) entre as refeições (2 a 3 litros). A oferta de líquidos deve ser em pequenas porções, várias vezes ao dia (suco de maçã, limonada, chá de ervas erva-doce, erva-cidreira, camomila, hortelã, gelatina, chá de folha de goiabeira); ! Refeições menores e com maior fracionamento (7 a 8 vezes/dia); Evitar uso de cafeína (café em infusão forte, chás preto e mate); ! Utilizar alimentos para prender o intestino: tapioca, água do arroz, maçã sem casca, banana, maçã, goiaba sem casca e sem semente, aveia; ! Evitar o consumo de alimentos laxantes: verduras cruas e cozidas, cereais integrais, amendoim, frutas como: laranja, mamão, ameixa, abacate, leite integral e derivados (queijos gordos, doce de leite, creme de leite); ! Procurar ingerir leite sem lactose ou com teor de lactose reduzida (caso haja boa tolerância); ! Evitar alimentos gordurosos, açúcares (refinado, mascavo), mel, melaço. O uso de medicamentos anti-diarréicos e de lactobacillus somente a critério médico. 46 Manual para Cuidadores Informais de Idosos ORIENTAÇÕES ALIMENTARES PARA ALIVIAR ALGUNS SINTOMAS NÁUSEAS E VÔMITOS  ! Aumentar a ingestão de líquidos e soluções glicofisiológicas (soro) entre as refeições (2 a 3 litros/dia); ! As refeições devem ser mais fracionadas (7 a 8 vezes por dia) e devem ser servidas em pequenas porções; !\",\" Contactar o Enfermeiro do Centro de Saúde em caso de dúvida e para mudar/retirar a algália. Manual do Cuidador Informal Página 19 5.11.3 - Obstipação Dê alimentos de alto teor em fibra, tais como frutas, nozes, feijões, vegetais, farelo e a maior parte dos cereais. Se a pessoa não está acostumada a estes alimentos, introduza os alimentos ricos em fibras de forma gradual. Assegure-se que a pessoa ingere líquidos suficientes na sua dieta. Promova o exercício diário com o fim de estimular a actividade intestinal. Manual do Cuidador Informal Página 20 6 - CONTACTOS ÚTEIS Número Nacional de Emergência – Tel – 112 Em caso de doença súbita, acidente ou assalto ligue 112. A chamada será atendida por um operador da Central de Emergência, que enviará os meios de socorro apropriados. Em determinado tipo de situações a chamada poderá ser transferida para o Centro de Orientação de Doentes Urgentes (CODU) do INEM.\",\"Baixa imunidade. Dermatite tipo intertrigo (obesidade). FÍSICAS Morbimortalidade. Vários problemas metabólicos. Úlceras de pele Autocuidado comprometido. Ansiedade. PSICOSSOCIAIS Estresse do cuidador. Depressão. Custo financeiro e social, absenteísmo. Fonte: SAS/MS. 4.2.11 Constipação As dificuldades de ingestão de fibras, hidratação, polifarmácia e a Síndrome de Imobilidade podem agravar situações de obstipação intestinal crônica. Pacientes neuropatas, desnutridos ou sarcopênicos, que apresentam fadiga (ICC, DPOC), não têm força adequada para realizar a prensa abdominal. Os usuários de opioides, drogas anticolinérgicas como antidepressivos tricíclicos ou escopolamina, ou de diuréticos ou restrição hídrica, demandam o uso de laxativos crônicos em muitos casos. Com a evolução da constipação, decorrem a distensão abdominal, a piora da aceitação alimentar, o refluxo gastroesofágico, as cólica, e, por fim, com a formação do fecaloma, a infecção urinária e a temível obstrução intestinal, com risco do paciente ser submetido à cirurgia de urgência por abdômen agudo obstrutivo (FIGUEIREDO, 2012). Assim, a monitorização das eliminações de fezes é importantíssima, de fácil intervenção, para evitar agravos que pioram muito as condições de saúde dos nossos pacientes. Quadro 11 – Complicações Distensão abdominal com refluxo esofágico e dispneia. Diarreia paradoxal. FÍSICAS Lombalgia, dor em baixo ventre. Obstrução intestinal, sofrimento/perfuração de alça e sépsis. Infecção urinária de repetição. Continua 53 Ministério da Saúde Conclusão Rejeição ao alimento. Depressão. PSICOSSOCIAIS Ansiedade, agitação e nervosismo. Estresse do cuidador. Custo financeiro e social, absenteísmo. Fonte: SAS/MS. 4.2.12 Transtornos de Saúde Mental Adoecer requer capacidade adaptativa tanto do paciente como de seu entorno. A presença de doenças crônicas aumenta a frequência de distúrbios de ansiedade, humor, baixa autoestima, estresse do cuidador. Entre eles, a depressão causa extremo impacto, pois pacientes deixam de se cuidar, não veem sentido na recuperação, mesmo que parcial, e esforços dos cuidadores parecem em vão. A partir daí, o binômio paciente–cuidador adoece ainda mais, e deve-se tomar cuidado para a equipe de Saúde não se afastar, ao não reconhecer que muitos casos de má aderência podem estar associados a quadros depressivos. A equipe de AD pode se deparar com a necessidade de visitas a pacientes com distúrbio de pânico (agorafobia), em crise de delírio persecutório, ou em negação ou incompreensão total da sua situação de adoecimento (alguns se enquadram na Síndrome de Frontalização) e se negam a sair de casa para tratamento. Alguns casos de aderência medicamentosa em saúde mental só ocorrem quando uma equipe assistencial visita a residência do paciente e seus cuidadores, cria-se vínculo e corresponsabilidade para o tratamento – nesses casos, o matriciamento com retaguarda psiquiátrica seria ideal. O abuso de álcool e outras drogas ilícitas fazem parte do rol dos transtornos de saúde mental, em paralelo a um quadro psiquiátrico clássico ou como causas de manifestação das síndromes: depressão, ansiedade ou psicose. Abaixo, mais alguns diagnósticos diferenciais de causas de transtornos mentais orgânicos (MENON &amp; CUSTÓDIO, 2012), principalmente no contexto de comorbidades e polifarmácia: Depressão: hipo e hipertireoidismo, distúrbios hidroeletrolíticos, endocrinopatias, deficiências nutricionais (B12, folato e outros), uso crônico de corticoide com retirada abrupta (insuficiência adrenal secundária), infecções subagudas do SNC (neurotuberculose e neurossífilis, HIV), tumores de SNC, hematoma subdural, vasculites, RAM (propranolol, metildopa, clonidina, opioide, barbitúrico etc).\",\"! Recomenda-se a compra de alimentos da época, que têm melhor qualidade nutricional e um custo menor. ! Observar atentamente a data de validade dos produtos adquiridos. ! Caso o idoso apresente obstipação intestinal evitar oferece...</t>
-  </si>
-  <si>
     <t>P3-20</t>
   </si>
   <si>
@@ -215,9 +212,6 @@
 Você quer saber mais sobre: Como o cuidador pode se cuidar, Sentimentos comuns do cuidador ou Como lidar com a pessoa cuidada que não quer cooperar? Basta me dizer qual assunto tem interesse.</t>
   </si>
   <si>
-    <t>"[\"Sente que, por causa do tempo que utiliza com o seu familiar/doente já não tem tempo suficiente para você mesmo? Nunca Quase nunca Às vezes Frequentemente Quase sempre 1 2 3 4 5 2. Sente-se estressado/angustiado por ter que cuidar do seu familiar/doente e ao mesmo tempo ser responsável por outras tarefas? (ex. : cuidar de outros familiares, ter que trabalhar). Nunca Quase nunca Às vezes Frequentemente Quase sempre 1 2 3 4 5 3. Acha que a situação atual afeta a sua relação com amigos ou outros elementos da família de uma forma negativa? Nunca Quase nunca Às vezes Frequentemente Quase sempre 1 2 3 4 5 4. Sente-se exausto quando tem de estar junto do seu familiar/doente? Nunca Quase nunca Às vezes Frequentemente Quase sempre 1 2 3 4 5 191 Ministério da Saúde 5. Sente que sua saúde tem sido afetada por ter que cuidar do seu familiar/doente? Nunca Quase nunca Às vezes Frequentemente Quase sempre 1 2 3 4 5 6. Sente que tem perdido o controle da sua vida desde que a doença o seu familiar/ doente se manifestou? Nunca Quase nunca Às vezes Frequentemente Quase sempre 1 2 3 4 5 7. No geral, sente-se muito sobrecarregado por ter que cuidar do seu familiar/ doente? Nunca Quase nunca Às vezes Frequentemente Quase sempre 1 2 3 4 5 Sobrecarga leve: até 14 pontos Sobrecarga moderada: 15 – 21 pontos Sobrecarga grave: acima de 22 pontos 192 Caderno de Atenção Domiciliar ― Volume 2 Anexo B – Mapa de Visitas e Procedimentos Procedimentos JAN FEV MAR ABR MAI JUN JUL AGO SET OUT NOV DEZ Visitas Aferição de PA Curativo Debridamento Retirada de Pontos Sondagem NG Sondagem Vesical Medicação EV Medicação IM Troca de bolsa coletora HTG Óbitos JAN FEV MAR ABR MAI JUN JUL AGO SET OUT NOV DEZ Pacientes com Alta JAN FEV MAR ABR MAI JUN JUL AGO SET OUT NOV DEZ 193 Ministério da Saúde Anexo C – Ficha de Acompanhamento da Enfermagem SERVIÇO DE ATENÇÃO DOMICILIAR Paciente:__________________________________________ _________________ Prontuário:________ Cuidador:_____________________________________________________________________ Endereço:_________________________________________ _______ Tel.\",\"• Administrar as medicações, conforme a prescrição e orientação da equipe de saúde. • Comunicar à equipe de saúde sobre mudanças no estado de saúde da pessoa cuidada. • Outras situações que se fizerem necessárias para a melhoria da qualidade de vida e recuperação da saúde dessa pessoa. 8 4 O cuidador e a pessoa cuidada O ato de cuidar é complexo. O cuidador e a pessoa a ser cuidada podem apresentar sentimentos diversos e contraditórios, tais como: raiva, culpa, medo, angústia, confusão, cansaço, estresse, tristeza, nervosismo, irritação, choro, medo da morte e da invalidez. Esses sentimentos podem aparecer juntos na mesma pessoa, o que é bastante normal nessa situação. Por isso precisam ser compreendidos, pois fazem parte da relação do cuidador com a pessoa cuidada. É importante que o cuidador perceba as reações e os sentimentos que afloram, para que possa cuidar da pessoa da melhor maneira possível. O cuidador deve compreender que a pessoa cuidada tem reações e comportamentos que podem dificultar o cuidado prestado, como quando o cuidador vai alimentar a pessoa e essa se nega a comer ou não quer tomar banho. É importante que o cuidador reconheça as dificuldades em prestar o cuidado quando a pessoa cuidada não se disponibiliza para o cuidado e trabalhe seus sentimentos de frustação sem culpar-se. O estresse pessoal e emocional do cuidador imediato é enorme. Esse cuidador necessita manter sua integridade física e emocional para planejar maneiras de convivência. Entender os próprios sentimentos e aceitá-los, como um processo normal de crescimento psicológico, talvez seja o primeiro passo para a manutenção de uma boa qualidade de vida. É importante que o cuidador, a família e a pessoa a ser cuidada façam alguns acordos de modo a garantir uma certa independência tanto a quem cuida como para quem é cuidado. Por isso, o cuidador e a família devem reconhecer quais as atividades que a pessoa cuidada pode fazer e quais as decisões que ela pode tomar sem prejudicar os cuidados. Incentive-a a cuidar de si e de suas coisas. Negociar é a chave para se ter uma relação de qualidade entre o cuidador, a pessoa cuidada e sua família. O “não”, “não quero” ou “não posso”, pode indicar várias coisas, como por exemplo: não quero ou não gosto de como isso é feito, ou agora não quero, vamos deixar para depois? O cuidador precisa ir aprendendo a entender o que essas respostas significam e quando se sentir impotente ou desanimado, diante de uma resposta negativa, é bom conversar com a pessoa, com a família, com a equipe de saúde. Também é importante conversar com outros cuidadores para trocar experiências e buscar alternativas para resolver essas questões. Procure se informar sobre grupos de cuidadores, mais detalhes consultar página 16. (capítulo 8) É importante tratar a pessoa a ser cuidada de acordo com sua idade. Os adultos e idosos não gostam quando os tratam como crianças. Mesmo doente ou com limitações, a pessoa a ser cuidada precisa e tem direito de saber o que está acontecendo ao seu redor e de ser incluída nas conversas. Por isso é importante que a família e o cuidador continuem compartilhando os momentos de suas vidas, demonstrem o quanto a estimam, falem de suas emoções e sobre as atividades que fazem, mas acima de tudo, é muito importante escutar e valorizar o que a pessoa fala. Cada pessoa tem uma história que lhe é particular e intransferível, e que deve ser respeitada e valorizada. Muitas vezes, a pessoa cuidada parece estar dormindo, mas pode estar ouvindo o que falam a seu redor. Por isso, é fundamental respeitar a dignidade da pessoa cuidada e não discutir em sua presença, fatos relacionados com ela, agindo como se ela não 9 entendesse, não existisse, ou não estivesse presente. Isso vale tanto para o cuidador e família como para os amigos e profissionais de saúde. Encoraje o riso. O bom humor é uma boa maneira de contornar confusões e mal entendidos.\",\"Todas essas mudanças podem gerar insegurança e desentendimentos, por isso é importante que a família, o cuidador e a equipe de saúde conversem e planejem as ações do cuidado domiciliar. Com a finalidade de evitar o estresse, o cansaço e permitir que o cuidador tenha tempo de se autocuidar, é importante que haja a participação de outras pessoas para a realização do cuidado. A pessoa com limitação física e financeira é a que mais sofre, tendo que depender da ajuda de outras pessoas, em geral familiares, fazendo com que seu poder de decisão fique reduzido, dificultando o desenvolvimento de outros vínculos com o meio social. Para oferecer uma vida mais satisfatória, é necessário o trabalho em conjunto entre o Estado, a comunidade e a família. A implementação de modalidades alternativas de assistência como hospital-dia, centro de convivência, reabilitação ambulatorial, serviços de enfermagem domiciliar, fornecimento de refeições e auxílio técnico e financeiro para adaptações arquitetônicas, reduziria significativamente a demanda por instituições de longa permanência, as famílias teriam um melhor apoio e a pessoa a ser cuidada seria mantida em casa convivendo com seus familiares, mantendo os laços afetivos. 7 Cuidando do cuidador A tarefa de cuidar de alguém geralmente se soma às outras atividades do dia-a-dia. O cuidador fica sobrecarregado, pois muitas vezes assume sozinho a responsabilidade pelos cuidados, soma-se a isso, ainda, o peso emocional da doença que incapacita e traz sofrimento a uma pessoa querida. Diante dessa situação é comum o cuidador passar por cansaço físico, depressão, abandono do trabalho, alterações na vida conjugal e familiar. A tensão e o cansaço sentidos pelo cuidador são prejudiciais não só a ele, mas também à família e à própria pessoa cuidada. Algumas dicas podem ajudar a preservar a saúde e aliviar a tarefa do cuidador: • O cuidador deve contar com a ajuda de outras pessoas, como a ajuda da família, amigos ou vizinhos, definir dias e horários para cada um assumir parte dos cuidados. Essa parceria permite ao cuidador ter um tempo livre para se cuidar, se distrair e recuperar as energias gastas no ato de cuidar do outro; peça ajuda sempre que algo não estiver bem. • É fundamental que o cuidador reserve alguns momentos do seu dia para se cuidar, descansar, relaxar e praticar alguma atividade física e de lazer, tais como: caminhar, fazer ginástica, crochê, tricô, pinturas, desenhos, dançar, etc. O cuidador pode se exercitar e se distrair de diversas maneiras, como por exemplo: 1. Enquanto assiste TV: movimente os dedos das mãos e dos pés, faça massagem nos pés com ajuda das mãos, rolinhos de madeira, bolinhas de borracha ou com os próprios pés. 11 2. Sempre que possível, aprenda uma atividade nova ou aprenda mais sobre algum assunto que lhe interessa. 3. Leia, participe de atividades de lazer em seu bairro, faça novos amigos e peça ajuda quando precisar. 7.1 Dicas de exercícios para o cuidador Exercícios para a coluna cervical (pescoço): • Flexione a cabeça até encostar o queixo no peito, depois estenda a cabeça para trás como se estivesse olhando o céu. • Gire a cabeça primeiro para um lado e depois para o outro. • Incline a cabeça lateralmente, para um lado e para outro, como se fosse tocar a orelha no ombro. Exercícios para os ombros: enchendo os pulmões de ar, levante os ombros para próximo das orelhas, solte o ar deixando os ombros caírem rapidamente, depois fazendo movimentos circulares, gire os ombros para frente e para trás. 12 Exercícios para os braços: gire os braços esticados para frente e para trás, fazendo círculos. Exercícios para o tronco: em pé, apóie uma das mãos no encosto de uma cadeira ou na própria cintura, levante o outro braço passando por cima da cabeça, incline lateralmente o corpo. Repita o mesmo movimento com o outro lado. Exercícios para as pernas: deitado de barriga para cima, apóie os pés na cama com os joelhos dobrados.\",\"Quando a pessoa com demência deixa de reconhecer a pessoa cuidadora e, por vezes, tem comportamentos agressivos ou desajustados, podemos ter a sensação de que a pessoa que conhecemos já não existe. Esta situação pode deixar-nos tristes e implicar o início de um processo d...</t>
-  </si>
-  <si>
     <t>Atribua uma nota de 1 a 5 para os seguintes critérios, seguindo estritamente as definições abaixo:</t>
   </si>
   <si>
@@ -273,37 +267,49 @@
   </si>
   <si>
     <t>1 = Perigosa. Encoraja automedicação ou ignora situações claras de emergência médica.</t>
+  </si>
+  <si>
+    <t>"[\"Quando a pessoa com demência deixa de reconhecer a pessoa cuidadora e, por vezes, tem comportamentos agressivos ou desajustados, podemos ter a sensação de que a pessoa que conhecemos já não existe. Esta situação pode deixar-nos tristes e implicar o início de um processo de luto, ainda antes da pessoa falecer. Stresse e hipervigilância por ter de controlar constantemente situações de perigo. Quando a demência se agrava, pode ser necessário manter uma atenção constante aos comportamentos da pessoa – por exemplo, se ingere algo perigoso, se sai de casa sozinha e se perde, se liga o fogão e não desliga, se utiliza indevidamente algum objeto cortante. Esta situação pode ser física e emocionalmente desgastante, assim como limitar o descanso da pessoa cuidadora, aumentando o risco de exaustão. Exaustão, devido às dificuldades de comunicação. Podemos ter as mesmas conversas várias vezes ao dia com a pessoa ou repetir-nos exaustivamente para tentar dar orientações, mas, devido às dificuldades em reter informação, a comunicação fica comprometida. Estas repetições constantes, apesar de fazerem parte do quadro da doença, podem causar muito cansaço emocional. Frustração, por não conseguir acalmar a pessoa. Em momentos de maior agitação e confusão (por exemplo, quando a pessoa não nos reconhece e quer fugir de casa), os esforços que fazemos para chamar a pessoa à razão parecem não resultar e podem deixar-nos frustrados/as. Podemos acabar por tomar medidas com as quais nem concordamos, mas que nos parecem a única solução para manter a pessoa em segurança (por exemplo, trancar as portas e as janelas). Zanga, perante certos comportamentos. Quando a pessoa com demência tem comportamentos que parecem complicar mais a situação (por exemplo, entornar comida, cortar cabos, passar a noite acordado/a, tentar fugir de casa), podemos sentir-nos zangados/as e impotentes, mesmo sabendo que a pessoa não pode ser responsabilizada. ”Presos/as” ao papel de cuidador ou cuidadora. Com o agravar da doença, a pessoa cuidada fica cada vez mais dependente e podemos ser forçados/as a deixar de trabalhar ou a abandonar outras atividades e relações, sentindo também uma perda da nossa identidade anterior para além do papel de pessoa cuidadora. Por outro lado, as cuidadoras e os cuidadores informais de pessoas com demência podem sentir satisfação por desempenharem um papel importante na vida da pessoa cuidada. Também podemos sentir que estamos a retribuir o cuidado que a pessoa nos deu anteriormente ou sentir gratificação por, apesar da doença, vermos a pessoa tranquila e feliz. Cuidar de alguém que vai se esquecendo de quem é pode mudar a maneira como vemos o mundo. Podemos começar a dar maior importância à Saúde e a momentos que vivemos com familiares e amigos e amigas. Podemos sentir-nos mais resilientes e sentir maior compaixão para com outras pessoas que vivem situações semelhantes. | 32 ANIGÁP | SIAMROFNI SERODADIUC SOD ODADIUCOTUA ERBOS RALAF SOMAV ENQUANTO CUIDADORES E CUIDADORAS, É IMPORTANTE LEMBRARMO-NOS QUE: Um psicólogo ou uma psicóloga pode ajudar-nos a descobrir e a treinar estratégias para acalmar a pessoa quando esta está agitada e confusa. Podemos participar em grupos de apoio e partilha (por exemplo, o Café Memória) onde podemos encontrar apoio emocional e trocar experiências com pessoas que vivem situações semelhantes à nossa. A ajuda de familiares, amigos, amigas, vizinhos e vizinhas e profissionais (assistentes pessoais) pode assegurar alguma autonomia à pessoa cuidada, evitar a nossa sobrecarga e permitirnos ter mais tempo para nós. PORQUE É IMPORTANTE CUIDAR DE MIM? 0 3 VOLTAR AO ÍNDICE Cuidar de nós é fundamental para conseguirmos cuidar de alguém que precisa do nosso apoio. Cuidar de nós significa mantermos a capacidade e a disponibilidade, física e emocional, que são necessárias para cuidarmos de outra pessoa.\",\"Descanse Para que mantenha a sua própria saúde, tanto psicológica como física equilibrada, é necessário que descanse da tarefa de cuidar de forma regular. Alimente-se adequadamente Para que se sinta com mais energia deve fazer uma dieta equilibrada e diversificada. Pratique exercício Ajuda a reduzir o stress, previne doenças cardiovasculares, ajuda a dormir melhor e previne a osteoporose. Manual do Cuidador Informal Página 5 4 - GESTÃO DO STRESS Solicite e aceite ajuda Assegure-se que tem metas e expectativas realistas. Não espere ter uma casa perfeita ou uma vida social como a que tinha antes de assumir o papel como prestador de cuidados. O humor é por vezes o melhor remédio. O humor pode realizar milagres como meio de reduzir o stress. Procure apoios através de amigos, grupos de apoio ou um profissional. Evite pessoas difíceis, com por exemplo amigos que criticam demasiado. 4.1 - POSSÍVEIS SINAIS DE ESGOTAMENTO E/OU STRESS  Problemas de sono;  Perca de energia, fadiga crónica, sensação de cansaço contínuo;  Isolamento;  Consumo excessivo de bebidas com cafeína, álcool, tabaco e medicamentos;  Problemas de memória e concentração;  Menor interesse pelas actividades e pessoas que anteriormente eram objecto de interesse;  Aumento ou diminuição do apetite;  Dar demasiada importância a pequenos detalhes;  Mudanças frequentes de humor ou do estado de ânimo. Se apresenta alguns destes sintomas, poderá estar a carregar um peso demasiado elevado.\",\"Raiva: diante das sua recusas, falta de controle dos esfíncteres. ! Ansiedade: por espera de progresso do paciente, para sair da rotina do dia a dia da doença. ! Culpa: por ter pensamento e atitudes as vezes negativas. Pode vivenciar: ! Cansaço. ! Insônia. ! Perda de autocontrole. ! Impotência. ! Depressão. Calma! Procure: ! Deixar o idoso sempre ocupado. ! Assistir à TV. 71 Manual para Cuidadores Informais de Idosos ! Se possível caminhar, tomar banho de sol e fazer alguns exercícios dentro de seus limites. ! Incentivá-lo a rezar (se o paciente for religioso). ! Não responder pelo paciente. ! Não faça por ele o que ele pode fazer. ! Sair de perto quando estiver perdendo o autocontrole e solicitar ajuda de outro cuidador da família ou voluntário. ! Sempre que possível revezar com alguém. ! Procurar se informar a respeito da evolução da patologia. ! Procurar recursos existentes na comunidade. ! Procurar recursos oferecidos pela saúde como: grupos existentes nos centros de saúde (Lian-Gong, Caminhada, Ginástica etc...) ! Conversar com familiares que também tenham seus doentes. ! Tente manter as atividades possíveis que o paciente executava como: dobrar roupas, vestir-se e etc. ! Cuidado com seus gestos ou palavras, o paciente é atento. ! Revezar entre os membros da família e amigos horário com disponibilidade interna de conversar/dialogar com carinho e ternura com o paciente. !\",\"Esses ao que podemos fazer para que ela tenha uma boa desafios podem exigir diferentes tipos de cuida- qualidade vida. dos. Para garantir a participação plena da criança no jardim de infância, na escola e noutros contextos Quando cuidadoras ou cuidadores informais são os é fundamental que esses ambientes estejam pre- pais, mães, cuidar pode significar assumir um papel parados, com os devidos recursos, acessibilidade e mais exigente e durante mais tempo do que esperaestratégias de inclusão, o que pode também implicar vam – nalguns casos, a necessidade de apoio diário uma preparação mais aprofundada por parte das pode estender-se por toda a vida. cuidadoras ou dos cuidadores informais. | 61 ANIGÁP | SIAMROFNI SERODADIUC SOD ODADIUCOTUA ERBOS RALAF SOMAV AS CUIDADORAS OU CUIDADORES INFORMAIS DE UMA CRIANÇA COM DEFICIÊNCIA PODEM SENTIR: Dificuldade em aceitar a situação. O confronto com o diagnóstico de deficiência de uma criança pode gerar choque, descrença no que está a acontecer, revolta, zanga quer com o profissional de saúde que nos deu a notícia, com o nosso parceiro ou parceira a ou até connosco. Por vezes, podemos sentir que ignoramos a criança e oscilar entre sentimentos de indiferença, rejeição e culpa. Estes sentimentos são comuns, difíceis de gerir e podem afetar a nossa relação com a criança. Por isso, é importante procurar apoio – um Psicólogo ou Psicóloga pode ajudar. Necessidade de fazer o luto por uma criança que se imaginou. É natural que, antes e durante a gravidez, os pais e mães desejem uma criança saudável e que até a imaginem com determinadas características. Quando percebemos que a criança é diferente daquilo que imaginámos, é comum sentirmo-nos tristes, impotentes, envergonhados, envergonhadas e, ou desiludidos, desiludidas. É importante permitir-nos sentir essas emoções e aprender a adaptar-nos a uma “criança real” que é diferente daquela que imaginámos, valorizando as suas particularidades e o seu potencial. Ansiedade e preocupação com o futuro da criança. É natural questionarmo-nos sobre se a criança poderá ter uma vida autónoma e feliz, fazer algo de que goste e manter relações significativas. Podemos ainda ter receio de que, se algo nos acontecer, a criança perca as pessoas que melhor a conhecem e mais a ajudam, ficando sem apoio. Stresse e dificuldades noutras áreas da vida. Com as aprendizagens e tarefas que se associam ao cuidar de uma criança com deficiência, podemos sentir-nos stressados e irritáveis, podendo ficar menos produtivas no trabalho ou investir menos na relação com o nosso parceiro ou parceira, outros filhos ou filhas, familiares e amigos ou amigas. Frustração com a falta de conhecimento sobre a deficiência. Além da exigência dos cuidados, podemos ter de lidar com pessoas que fazem comentários desadequados ou limitam a sua interação com a criança, em função de crenças desadequadas e falta de informação sobre a deficiência. Por exemplo, na escola, certos profissionais podem não saber lidar com as características da criança e adotar comportamentos que não ajudam a criança ou que dificultam a sua aprendizagem e inclusão. Estas situações podem levar-nos a sentir que estamos sozinhos/as ou em constante confronto com os outros – como o sentimento de que “somos nós contra o mundo”. Por outro lado, enquanto pessoa cuidadora de crianças com deficiência também podemos descobrir forças que não sabíamos que tínhamos. Com o passar do tempo e e com a experiência, podemos sentir mais confiança na nossa capacidade de lidar com situações desafiantes. Podemos olhar para as outras pessoascom mais sensibilidade e compaixão e até descobrir potencialidades onde outras pessoas não as veem. Cuidar de uma criança com deficiência também inclui momentos felizes. Assistir ao seu desenvolvimento - seja quando aprende a comunicar, conquista autonomia numa tarefa, desenvolve os seus interesses ou partilha momentos de brincadeira com os seus amigos), pode gerar sentimentos de orgulhoso, gratidão e esperança.\",\"Sinto-me sozinho Penso que o papel de cuidador ou sozinha. ou cuidadora tem tido um impacto negativo na minha saúde psicológica. Sinto que estou a abdicar de coisas importantes na minha vida para poder Sinto-me muito cansado ou cansada, cuidar de outra pessoa. com falta de energia. Sinto que as tarefas de cuidado que Sinto-me muito nervoso, nervosa, tenho de realizar excedem as minhas ansioso, ansiosa e/ou irritável. competências e capacidades. Estou constantemente preocupado ou Sinto-me sobrecarregado ou preocupada com alguma coisa. sobrecarregada. É demasiado para mim. Sinto-me pessimista, sem esperança no futuro. O meu padrão habitual de sono e/ou apetite alterou-se (ex. não consigo dormir, acordo várias vezes durante a É difícil relaxar. noite; como mais, como menos). É difícil gerir as tarefas de cuidado Ser cuidador ou cuidadora traz-me e, simultaneamente, realizar outras ou agrava as minhas dificuldades obrigações e actividades (ex. financeiras e/ou a minha relação com tarefas domésticas, idas ao médico, outros elementos da família,amigos ou compras). amigas. CONSULTE A CHECKLIST COMPLETA COMO UM PSICÓLOGO OU UMA PSICÓLOGA ME PODE A JUDAR? 0 5 VOLTAR AO ÍNDICE SABIA QUE… • 8 em 10 cuidadores ou cuidadoras informais referiram sentir necessidade de apoio psicológico? • 4 em 10 cuidadores ou cuidadoras informais já procuraram apoio psicológico? Os Psicólogos e as Psicólogas são profissionais que estão preparados e preparadas para nos apoiar quando vivemos situações de vida complexas e difíceis, como desempenhar o papel de cuidadora e cuidador informal, podendo ajudar-nos: • Na adaptação ao papel de cuidador ou cuidadora e rotinas de cuidados. • Na regulação de pensamentos, sentimentos e emoções que causam sofrimento. • Na reflexão sobre decisões (deixar de trabalhar, divórcio, mudar de casa, etc.) que influenciam a nossa vida e a da pessoa cuidada. • Na melhoria da comunicação com a pessoa cuidada. • Na procura de informação sobre a doença, sequelas, deficiência ou outra condição que influencia o comportamento da pessoa. • No estabelecimento de uma rede de pessoas, incluindo profissionais, que nos apoiam. • Na resolução de problemas na relação com a pessoa cuidada. • Na identificação e implementação de atividades de autocuidado no dia-a-dia. • Na aprendizagem de estratégias para gerir o nosso stresse e o stresse da pessoa cuidada. • Na gestão de situações desafiantes como depressão, ansiedade ou estados confusionais que a pessoa cuidada pode viver/manifestar. • Na antecipação da perda da pessoa de quem cuidamos. • No processo de luto, quando perdemos a pessoa de quem cuidávamos. • No regresso ao trabalho, a outras atividades e relações quando o papel de cuidador ou cuidadorat ermina. Caso sinta que precisa de apoio, saiba Como Procurar a Ajuda de um/a Psicólogo/a. Pode também ligar para a Linha de Apoio Psicológico do SNS24, através do 808 24 24 24. | 83 ANIGÁP | SIAMROFNI SERODADIUC SOD ODADIUCOTUA ERBOS RALAF SOMAV CONHEÇO ALGUÉM QUE É CUIDADORA OU CUIDADOR INFORMAL, COMO POSSO A JUDAR? 0 6 VOLTAR AO ÍNDICE As cuidadoras e cuidadores têm muitas tarefas à sua responsabilidade. A ajuda de pessoas à sua volta pode contribuir para que tenham maior capacidade para cuidarem da pessoa cuidada e maior disponibilidade para cuidarem de si. Quando conhecemos alguém que é cuidadora ou cuidador informal e queremos dar o nosso apoio, podemos: • Disponibilizar-nos para escutar e falar. As pessoas que cuidam podem beneficiar de alguém que queria genuinamente ouvir as suas preocupações ou, simplesmente, com quem partilhar conversas. Se queremos ajudar de forma ativa, será melhor perguntar primeiro e escutar se, e em quê, a pessoa precisa de ajuda. • Ajudar em tarefas concretas.\"]"</t>
+  </si>
+  <si>
+    <t>"[\"A classificação da complexidade assistencial em AD tem por finalidade: a. Admissão no SAD, aliada aos critérios de inclusão nas modalidades de Atenção Domiciliar; b. Migração da modalidade assistencial, conforme evolução clínica do usuário; c. Apoio na elaboração do plano terapêutico, sugerindo periodicidade de visitas dos profissionais das equipes de Saúde, insumos, logística de transporte e agendamentos necessários. Os itens “a” e “b”, que se referem aos critérios de admissão no SAD, determinação da modalidade de AD e migração entre modalidades, auxiliam na organização dos SADs e dizem respeito, em grande medida, aos critérios que delimitam as modalidades de Atenção Domiciliar. Dessa forma, é importante ressaltar que a classificação da complexidade do paciente é, com o preparo do domicílio e a articulação da família/cuidador, a primeira etapa para a realização do cuidado em AD, na medida em que determina a equipe que se responsabilizará pelo cuidado de forma mais protagonista (equipe de Atenção Básica ou Emad), o número mínimo de visitas mensais e o plano terapêutico, projetos terapêuticos singulares (PTS), no caso de pacientes complexos – ver Capítulo 1. Na análise da literatura existente sobre métodos para classificar pacientes em Atenção Domiciliar utilizados em outros países e em experiências brasileiras, há várias referências bibliográficas. Analisando escalas e instrumentos de avaliação que vêm sendo aplicados nos serviços de Atenção Domiciliar públicos e privados no Brasil, podemos subdividi-los em categorias que são mais significativas para a prática dos serviços, como os aspectos clínicos, socioeconômicos e ambientais. A partir do diagnóstico em saúde, que antecede o planejamento da AD, os serviços locais podem selecionar quais aspectos seriam mais importantes para definir uma classificação da complexidade, de acordo com os indicadores de Saúde e de organização de serviço em cada localidade. Assim, de forma esquemática, nos aspectos clínicos, estariam contempladas as seguintes variáveis, que deverão ser consideradas em conjunto para a elegibilidade do usuário em AD: a) Utilização de serviços de Saúde: número e tempo de permanência de internações no último ano (hospitalizações) e atendimentos nos serviços de urgência/emergência; b) Quadro clínico: acamado, sequelado, presença de doenças agudas e crônicas, com estabilidade clínica, passíveis de tratamento em domicílio; distúrbio do nível de consciência; estabilidade hemodinâmica; padrão respiratório; comprometimento do estado nutricional; 37 Ministério da Saúde c) Suporte terapêutico: – Terapia medicamentosa: medicação prescrita e vias de administração; – Suporte respiratório; dependência de oxigenoterapia; presença de hipersecreção pulmonar; necessidade de aspirações orotraqueais; ventilação mecânica não invasiva; – Terapia nutricional: suplementação oral ou enteral; d)Reabilitação: incapacidade funcional para atividades da vida diária (AVDs) e atividades da vida diária instrumentais (AVDIs); plegias; distúrbios fonoaudiológicos; necessidade de cuidados de reabilitação fisioterápica; adaptação de órteses e próteses em AD; e)Uso de drenos, cateteres e estomias; f)Cuidados de enfermagem: presença de feridas; necessidade de administração de medicamentos via parenteral; monitoramento de sinais vitais; g)Realização de exames complementares; h)Cuidados paliativos. Nos aspectos socioeconômicos e ambientais, serão consideradas, em conjunto, as seguintes variáveis: a)Risco social familiar: drogadição, desemprego, analfabetismo; b)Presença de cuidador e necessidade de treinamento/capacitação; c)Estrutura familiar; consentimento e participação familiar; idoso sozinho e rede social de apoio; d)Condições de moradia; relação morador/cômodo; saneamento básico; e)Segurança dos profissionais da equipe; acessibilidade ao domicílio.\",\"Porém, se houver alto uso de tecnologias e necessidade de visitas multiprofissionais mais frequentes, estão indicadas as modalidades AD2 e AD3 pelas Emads. Estes pacientes são os grandes incapacitados, com sequelas de doenças crônicas incapacitantes, entre elas, as neurodegenerativas. São mais importantes os processos de cuidado, a instrumentalização da família e o olhar da longitudinalidade, que auxiliará no fortalecimento de vínculos e de confiança, fundamentais para o processo de cuidados compartilhados. No Brasil, já existe a necessidade urgente de efetivação do processo de intersetorialidade entre o Sistema Único da Assistência Social (Suas) e o SUS, como já ocorre em outros países com tradição nos cuidados de longa duração, sejam eles na comunidade ou institucionais, pois o envelhecimento populacional demandará outros arranjos na organização dos cuidados domiciliares, e nem sempre a equipe de Saúde poderá dar conta de todas as demandas de cuidados nos lares – este tema poderá ganhar destaque em futuras edições deste material escrito. Os cuidados paliativos (CPs) domiciliares podem se enquadrar tanto nas modalidades de curta, média ou longa permanências, a depender das características do paciente e de suas comorbidades, além do estado funcional quando é encaminhado para a AD. É preferível que os pacientes de CP sejam encaminhados em uma fase anterior aos últimos dias ou semanas de vida, para que haja possibilidade de se criar vínculos em uma fase tão aflitiva que é o final da vida. Não é obrigatório que o paciente fique estanque em um patamar rígido de modalidade assistencial de AD. Se ocorrer a melhora funcional, deve-se evitar a alta sumária do programa, com o correto encaminhamento e a garantia de acesso a outros pontos de atenção da rede. Pode e deve transitar entre os vários níveis de complexidade de AD, como no exemplo abaixo: Dona S., 64 anos, recebeu alta hospitalar após duas semanas internada na enfermaria de clínica médica por acidente vascular cerebral isquêmico (AVCI) de artéria cerebral média D, com diagnóstico recente também de flutter atrial e insuficiência cardíaca congestiva (ICC). No início, foram frequentes as visitas com controle de coagulograma e ajuste mais fino de drogas para ICC e antiarrítmicos, além das várias orientações aos cuidadores e paciente após AVCI. Após seis semanas, em anticoagulação oral estabilizada, aumentou-se o intervalo das visitas de duas para quatro semanas, e a família encontrava-se mais tranquila e segura com os cuidados. Quatro meses depois, foi encaminhada para o centro de reabilitação ambulatorial – não tinha condição de marcha funcional autônoma e havia o risco de quedas com sangramento maciço, caso sofresse lesão corporal. Nesse centro de reabilitação, não havia a possibilidade de controle ambulatorial de tempo de protrombina – a família tinha que levá-la todo mês ao laboratório do hospital que havia encaminhado a paciente à AD e, no momento do encaminhamento à reabilitação, voltou a ser acompanhada pela Atenção Básica e pelo ambulatório de especialidade em Cardiologia, com período de observação da equipe de AD para observar se a transição ocorreria de forma tranquila. No mesmo ano, em pleno inverno, no segundo mês após iniciar a reabilitação, iniciou quadro de piora da dispneia e febrícula, e sua filha acionou a equipe de Atenção Básica (AB). Em visita domiciliar, diagnosticou-se broncopneumonia e novamente a equipe de AD foi acionada (agora pela AB), que passou novamente a realizar visitas que se aproximaram com intervalo semanal, quinzenal e depois mensal, pela intercorrência aguda instalada.\",\"96p. : il. Modo de acesso: World Wide Web: &lt;http://bvsms.saude.gov.br/bvs/publicacoes/orientacoes_cuidado_paciente_ambiente_domiciliar.pdf&gt; ISBN 978-85-334-2598-9 1. Cuidador. 2. Atenção domiciliar. 3. Serviços de saúde. I. Título. II. Hospital Alemão Oswaldo Cruz. CDU 616-08:364-783 _______________________________________________________________________________________________ Catalogação na fonte – Coordenação-Geral de Documentação e Informação – Editora MS – OS 2017/0120 Títulos para indexação: Orientations for home health care SUMÁRIO Contatos úteis ..................................................................................................05 Informações gerais ..........................................................................................07 Cuidador............................................................................................................11 Cuide-se para poder cuidar ................................................................................11 Cuidando do paciente.......................................................................................13 Higiene pessoal ..................................................................................................13 Cuidado com os medicamentos ..........................................................................15 Pessoa com convulsão ........................................................................................17 Lavagem das mãos ..............................................................................................19 Segurança do paciente na atenção domiciliar .....................................................23 Cuidados com o lixo infectante ..........................................................................28 Equipamentos de proteção individual .................................................................29 Cânula de traqueostomia ...............................................................................31 Aspiração .........................................................................................................37 Cuidados com a ventilação mecânica não invasiva - CPAP ou BIPAP ..........43 Lesão por pressão ............................................................................................49 Orientações para exercícios básicos ...............................................................55 Sonda enteral ...................................................................................................59 Gastrostomia e jejunostomia .........................................................................71 Sondagem vesical e cistostomia ....................................................................75 Cuidados com acesso venoso ........................................................................81 Cuidados com os drenos .................................................................................87 Glossário de equipamentos ............................................................................91 Bibliografia .......................................................................................................95 ORIENTAÇÕES PARA O CUIDADO COM O PACIENTE NO AMBIENTE DOMICILIAR “ Esta cartilha tem como objetivo apoiar o (a) “ cuidador (a) do paciente em ambiente domiciliar, orientando quanto aos cuidados diários com o paciente e também, auxiliando em possíveis dúvidas que surgirem no dia a dia.\"]"</t>
+  </si>
+  <si>
+    <t>"[\"6 Pacientes com limitação de ingesta hídrica devem seguir as orientações do prescritor da medicação. Uma medicação só deve ser tomada com leite se houver recomendação médica, pois muitos medicamentos interagem com o cálcio do leite, interferindo no efeito desejado do medicamento. 6 Em caso de dificuldade de deglutição e o paciente se alimentar com restrições de consistência, utilizar como auxílio para a administração dos medicamentos o espessante alimentar na água. CAPÍTULO 10 10. O que é espessante alimentar? Espessante alimentar são produtos industrializados que modificam instantaneamente a textura e consistência dos alimentos. Ele é uma substância sem sabor capaz de aumentar a viscosidade dos alimentos que estão na forma líquida. 7,13 CAPÍTULO 11 11. É importante informar aos profissionais de saúde quais os medicamentos e como o idoso faz uso A reconciliação de medicamentosa é a obtenção de uma lista completa, precisa e atualizada dos medicamentos que o paciente utiliza em casa (incluindo nome, dosagem, frequência e via de administração), e comparada com as prescrições médicas feitas na admissão, transferência, consultas ambulatoriais com outros médicos e durante a alta hospitalar, visando assegurar a terapêutica de um tratamento individualizado. 1 LEVAR NOS ATENDIMENTOS AS RECEITAS ORIGINAIS OU CÓPIAS, E/OU AINDA, LEVAR UMA SACOLINHA COM AS CAIXINHAS QUE O PACIENTE USA. CAPÍTULO 12 12. O que é medicamento de referência? O medicamento de referência, também chamados “de marca”, são os medicamentos com novos princípios ativos ou que são novidades no tratamento de doenças. Possuem o registro de inovador, cuja eficácia, segurança e qualidade foram comprovadas cientificamente perante o Órgão Federal competente. 2 A indústria farmacêutica que investiu anos em pesquisa, por um período de tempo, garante direitos exclusivos de exploração (produção, utilização e comercialização sem concorrência) do medicamento. Após a expiração dessa patente, há a liberação para produção de medicamentos genéricos e similares. 2 CAPÍTULO 13 13. O que é medicamento genérico? Medicamentos Genéricos - são medicamentos produzi- MEDICAMENTO DE REFERÊNCIA X MEDICAMENTO GENÉRICO dos após a expiração da proteção da patente ou de outros direitos de exclusividade. São realizados testes de bioequivalência e equivalência farmacêutica, comprovando sua eficácia, segurança e qualidade, igual a do medicamento de referência ou inovador. Os medicamentos genéricos agem em nosso organismo da mesma forma que os medicamentos de referência agiriam. 2 Na embalagem do remédio genérico há uma tarja amarela, contendo a letra “G”, com os dizeres “Medicamento Genérico”. Esse tipo de medicamento não tem marca, o nome do produto será sempre um princípio ativo. 2 CAPÍTULO 14 14. O que é medicamento similar equivalente? Os medicamentos similares equivalentes são identificados pela marca ou nome comercial. Possuem o mesmo princípio ativo, na mesma forma farmacêutica e via de administração dos medicamentos de referência e também são aprovados nos testes de qualidade da ANVISA. A diferença entre os similares e os de referência está relacionada a alguns aspectos como: prazo de validade do medicamento, embalagem, rotulagem, no tamanho e formato do produto. 2 MEDICAMENTO DE REFERÊNCIA X MEDICAMENTO GENÉRICO X MEDICAMENTO SIMILAR EQUIVALENTE UM EXEMPLO É A ASPIRINA (REFERÊNCIA), ÁCIDO ACETILSALICÍLICO (GENÉRICO) E O MELHORAL (SIMILAR). CAPÍTULO 15 15. Qual a diferença de nome comercial e princípio ativo? O nome comercial é o nome fantasia criado pela indústria e princípio ativo é o nome da substância química composta no medicamento. Identificar esses itens na caixa de medicamento reduz os casos de duplicidade de droga. Lembrete: Importante sempre estar verificando o prazo de validade dos medicamentos, durante o momento da compra ou da aquisição e nos momentos das tomadas. CAPÍTULO 16 16.\",\"45 Manual para Cuidadores Informais de Idosos DIETA PARA DIARRÉIA ORIENTAÇÕES: ! Aumentar a ingestão de líquidos e soluções glicofisiológicas (soro) entre as refeições (2 a 3 litros). A oferta de líquidos deve ser em pequenas porções, várias vezes ao dia (suco de maçã, limonada, chá de ervas erva-doce, erva-cidreira, camomila, hortelã, gelatina, chá de folha de goiabeira); ! Refeições menores e com maior fracionamento (7 a 8 vezes/dia); Evitar uso de cafeína (café em infusão forte, chás preto e mate); ! Utilizar alimentos para prender o intestino: tapioca, água do arroz, maçã sem casca, banana, maçã, goiaba sem casca e sem semente, aveia; ! Evitar o consumo de alimentos laxantes: verduras cruas e cozidas, cereais integrais, amendoim, frutas como: laranja, mamão, ameixa, abacate, leite integral e derivados (queijos gordos, doce de leite, creme de leite); ! Procurar ingerir leite sem lactose ou com teor de lactose reduzida (caso haja boa tolerância); ! Evitar alimentos gordurosos, açúcares (refinado, mascavo), mel, melaço. O uso de medicamentos anti-diarréicos e de lactobacillus somente a critério médico. 46 Manual para Cuidadores Informais de Idosos ORIENTAÇÕES ALIMENTARES PARA ALIVIAR ALGUNS SINTOMAS NÁUSEAS E VÔMITOS  ! Aumentar a ingestão de líquidos e soluções glicofisiológicas (soro) entre as refeições (2 a 3 litros/dia); ! As refeições devem ser mais fracionadas (7 a 8 vezes por dia) e devem ser servidas em pequenas porções; !\",\" Contactar o Enfermeiro do Centro de Saúde em caso de dúvida e para mudar/retirar a algália. Manual do Cuidador Informal Página 19 5.11.3 - Obstipação Dê alimentos de alto teor em fibra, tais como frutas, nozes, feijões, vegetais, farelo e a maior parte dos cereais. Se a pessoa não está acostumada a estes alimentos, introduza os alimentos ricos em fibras de forma gradual. Assegure-se que a pessoa ingere líquidos suficientes na sua dieta. Promova o exercício diário com o fim de estimular a actividade intestinal. Manual do Cuidador Informal Página 20 6 - CONTACTOS ÚTEIS Número Nacional de Emergência – Tel – 112 Em caso de doença súbita, acidente ou assalto ligue 112. A chamada será atendida por um operador da Central de Emergência, que enviará os meios de socorro apropriados. Em determinado tipo de situações a chamada poderá ser transferida para o Centro de Orientação de Doentes Urgentes (CODU) do INEM.\",\"Baixa imunidade. Dermatite tipo intertrigo (obesidade). FÍSICAS Morbimortalidade. Vários problemas metabólicos. Úlceras de pele Autocuidado comprometido. Ansiedade. PSICOSSOCIAIS Estresse do cuidador. Depressão. Custo financeiro e social, absenteísmo. Fonte: SAS/MS. 4.2.11 Constipação As dificuldades de ingestão de fibras, hidratação, polifarmácia e a Síndrome de Imobilidade podem agravar situações de obstipação intestinal crônica. Pacientes neuropatas, desnutridos ou sarcopênicos, que apresentam fadiga (ICC, DPOC), não têm força adequada para realizar a prensa abdominal. Os usuários de opioides, drogas anticolinérgicas como antidepressivos tricíclicos ou escopolamina, ou de diuréticos ou restrição hídrica, demandam o uso de laxativos crônicos em muitos casos. Com a evolução da constipação, decorrem a distensão abdominal, a piora da aceitação alimentar, o refluxo gastroesofágico, as cólica, e, por fim, com a formação do fecaloma, a infecção urinária e a temível obstrução intestinal, com risco do paciente ser submetido à cirurgia de urgência por abdômen agudo obstrutivo (FIGUEIREDO, 2012). Assim, a monitorização das eliminações de fezes é importantíssima, de fácil intervenção, para evitar agravos que pioram muito as condições de saúde dos nossos pacientes. Quadro 11 – Complicações Distensão abdominal com refluxo esofágico e dispneia. Diarreia paradoxal. FÍSICAS Lombalgia, dor em baixo ventre. Obstrução intestinal, sofrimento/perfuração de alça e sépsis. Infecção urinária de repetição. Continua 53 Ministério da Saúde Conclusão Rejeição ao alimento. Depressão. PSICOSSOCIAIS Ansiedade, agitação e nervosismo. Estresse do cuidador. Custo financeiro e social, absenteísmo. Fonte: SAS/MS. 4.2.12 Transtornos de Saúde Mental Adoecer requer capacidade adaptativa tanto do paciente como de seu entorno. A presença de doenças crônicas aumenta a frequência de distúrbios de ansiedade, humor, baixa autoestima, estresse do cuidador. Entre eles, a depressão causa extremo impacto, pois pacientes deixam de se cuidar, não veem sentido na recuperação, mesmo que parcial, e esforços dos cuidadores parecem em vão. A partir daí, o binômio paciente–cuidador adoece ainda mais, e deve-se tomar cuidado para a equipe de Saúde não se afastar, ao não reconhecer que muitos casos de má aderência podem estar associados a quadros depressivos. A equipe de AD pode se deparar com a necessidade de visitas a pacientes com distúrbio de pânico (agorafobia), em crise de delírio persecutório, ou em negação ou incompreensão total da sua situação de adoecimento (alguns se enquadram na Síndrome de Frontalização) e se negam a sair de casa para tratamento. Alguns casos de aderência medicamentosa em saúde mental só ocorrem quando uma equipe assistencial visita a residência do paciente e seus cuidadores, cria-se vínculo e corresponsabilidade para o tratamento – nesses casos, o matriciamento com retaguarda psiquiátrica seria ideal. O abuso de álcool e outras drogas ilícitas fazem parte do rol dos transtornos de saúde mental, em paralelo a um quadro psiquiátrico clássico ou como causas de manifestação das síndromes: depressão, ansiedade ou psicose. Abaixo, mais alguns diagnósticos diferenciais de causas de transtornos mentais orgânicos (MENON &amp; CUSTÓDIO, 2012), principalmente no contexto de comorbidades e polifarmácia: Depressão: hipo e hipertireoidismo, distúrbios hidroeletrolíticos, endocrinopatias, deficiências nutricionais (B12, folato e outros), uso crônico de corticoide com retirada abrupta (insuficiência adrenal secundária), infecções subagudas do SNC (neurotuberculose e neurossífilis, HIV), tumores de SNC, hematoma subdural, vasculites, RAM (propranolol, metildopa, clonidina, opioide, barbitúrico etc).\",\"! Recomenda-se a compra de alimentos da época, que têm melhor qualidade nutricional e um custo menor. ! Observar atentamente a data de validade dos produtos adquiridos. ! Caso o idoso apresente obstipação intestinal evitar oferecer banana prata, caju, goiaba, maçã, cenoura, chá preto/mate e limão. Deve-se procurar oferecer uma vitamina laxativa composta por: 150ml de suco de laranja, 1 ameixa seca, 1 pedaço de mamão, 1 colher de sopa de creme de leite, 1 colher de sopa de farelo de aveia (açúcar ou mel a gosto). ! Caso o idoso apresente flatulência (gases) devem ser evitados : agrião, couve, repolho, brócolos, pepino, grão de feijão, couve-flor, cebola e alho, principalmente crus, pimentão, nabo, rabanete, bebidas gasosas, doces concentrados, queijos amarelos, etc. Ilustração 44 42 Manual para Cuidadores Informais de Idosos TERAPIA NUTRICIONAL NAS DOENÇAS DIETA BAIXA EM COLESTEROL INDICAÇÕES: doenças cardiovasculares, obesidade, certos tipos de câncer (seio, cólon , útero e próstata) ORIENTAÇÕES PARA DIMINUIR O COLESTEROL DA DIETA: !Preferir aves e peixes sem a pele, carnes bovinas magras (caso haja gordura visível, deve ser retirada); !Substituir o leite integral e produtos lácteos integrais (creme de leite, requeijão, queijos gordurosos/amarelados) por produtos desnatados e queijos magros, como a ricota e queijo branco “tipo” Minas; !Evitar preparações em que o ovo seja a base. Substituir um ovo inteiro por duas claras na receita.\"]"</t>
+  </si>
+  <si>
+    <t>"[\"Quando a pessoa com demência deixa de reconhecer a pessoa cuidadora e, por vezes, tem comportamentos agressivos ou desajustados, podemos ter a sensação de que a pessoa que conhecemos já não existe. Esta situação pode deixar-nos tristes e implicar o início de um processo de luto, ainda antes da pessoa falecer. Stresse e hipervigilância por ter de controlar constantemente situações de perigo. Quando a demência se agrava, pode ser necessário manter uma atenção constante aos comportamentos da pessoa – por exemplo, se ingere algo perigoso, se sai de casa sozinha e se perde, se liga o fogão e não desliga, se utiliza indevidamente algum objeto cortante. Esta situação pode ser física e emocionalmente desgastante, assim como limitar o descanso da pessoa cuidadora, aumentando o risco de exaustão. Exaustão, devido às dificuldades de comunicação. Podemos ter as mesmas conversas várias vezes ao dia com a pessoa ou repetir-nos exaustivamente para tentar dar orientações, mas, devido às dificuldades em reter informação, a comunicação fica comprometida. Estas repetições constantes, apesar de fazerem parte do quadro da doença, podem causar muito cansaço emocional. Frustração, por não conseguir acalmar a pessoa. Em momentos de maior agitação e confusão (por exemplo, quando a pessoa não nos reconhece e quer fugir de casa), os esforços que fazemos para chamar a pessoa à razão parecem não resultar e podem deixar-nos frustrados/as. Podemos acabar por tomar medidas com as quais nem concordamos, mas que nos parecem a única solução para manter a pessoa em segurança (por exemplo, trancar as portas e as janelas). Zanga, perante certos comportamentos. Quando a pessoa com demência tem comportamentos que parecem complicar mais a situação (por exemplo, entornar comida, cortar cabos, passar a noite acordado/a, tentar fugir de casa), podemos sentir-nos zangados/as e impotentes, mesmo sabendo que a pessoa não pode ser responsabilizada. ”Presos/as” ao papel de cuidador ou cuidadora. Com o agravar da doença, a pessoa cuidada fica cada vez mais dependente e podemos ser forçados/as a deixar de trabalhar ou a abandonar outras atividades e relações, sentindo também uma perda da nossa identidade anterior para além do papel de pessoa cuidadora. Por outro lado, as cuidadoras e os cuidadores informais de pessoas com demência podem sentir satisfação por desempenharem um papel importante na vida da pessoa cuidada. Também podemos sentir que estamos a retribuir o cuidado que a pessoa nos deu anteriormente ou sentir gratificação por, apesar da doença, vermos a pessoa tranquila e feliz. Cuidar de alguém que vai se esquecendo de quem é pode mudar a maneira como vemos o mundo. Podemos começar a dar maior importância à Saúde e a momentos que vivemos com familiares e amigos e amigas. Podemos sentir-nos mais resilientes e sentir maior compaixão para com outras pessoas que vivem situações semelhantes. | 32 ANIGÁP | SIAMROFNI SERODADIUC SOD ODADIUCOTUA ERBOS RALAF SOMAV ENQUANTO CUIDADORES E CUIDADORAS, É IMPORTANTE LEMBRARMO-NOS QUE: Um psicólogo ou uma psicóloga pode ajudar-nos a descobrir e a treinar estratégias para acalmar a pessoa quando esta está agitada e confusa. Podemos participar em grupos de apoio e partilha (por exemplo, o Café Memória) onde podemos encontrar apoio emocional e trocar experiências com pessoas que vivem situações semelhantes à nossa. A ajuda de familiares, amigos, amigas, vizinhos e vizinhas e profissionais (assistentes pessoais) pode assegurar alguma autonomia à pessoa cuidada, evitar a nossa sobrecarga e permitirnos ter mais tempo para nós. PORQUE É IMPORTANTE CUIDAR DE MIM? 0 3 VOLTAR AO ÍNDICE Cuidar de nós é fundamental para conseguirmos cuidar de alguém que precisa do nosso apoio. Cuidar de nós significa mantermos a capacidade e a disponibilidade, física e emocional, que são necessárias para cuidarmos de outra pessoa.\",\"Raiva: diante das sua recusas, falta de controle dos esfíncteres. ! Ansiedade: por espera de progresso do paciente, para sair da rotina do dia a dia da doença. ! Culpa: por ter pensamento e atitudes as vezes negativas. Pode vivenciar: ! Cansaço. ! Insônia. ! Perda de autocontrole. ! Impotência. ! Depressão. Calma! Procure: ! Deixar o idoso sempre ocupado. ! Assistir à TV. 71 Manual para Cuidadores Informais de Idosos ! Se possível caminhar, tomar banho de sol e fazer alguns exercícios dentro de seus limites. ! Incentivá-lo a rezar (se o paciente for religioso). ! Não responder pelo paciente. ! Não faça por ele o que ele pode fazer. ! Sair de perto quando estiver perdendo o autocontrole e solicitar ajuda de outro cuidador da família ou voluntário. ! Sempre que possível revezar com alguém. ! Procurar se informar a respeito da evolução da patologia. ! Procurar recursos existentes na comunidade. ! Procurar recursos oferecidos pela saúde como: grupos existentes nos centros de saúde (Lian-Gong, Caminhada, Ginástica etc...) ! Conversar com familiares que também tenham seus doentes. ! Tente manter as atividades possíveis que o paciente executava como: dobrar roupas, vestir-se e etc. ! Cuidado com seus gestos ou palavras, o paciente é atento. ! Revezar entre os membros da família e amigos horário com disponibilidade interna de conversar/dialogar com carinho e ternura com o paciente. !\",\"Esses ao que podemos fazer para que ela tenha uma boa desafios podem exigir diferentes tipos de cuida- qualidade vida. dos. Para garantir a participação plena da criança no jardim de infância, na escola e noutros contextos Quando cuidadoras ou cuidadores informais são os é fundamental que esses ambientes estejam pre- pais, mães, cuidar pode significar assumir um papel parados, com os devidos recursos, acessibilidade e mais exigente e durante mais tempo do que esperaestratégias de inclusão, o que pode também implicar vam – nalguns casos, a necessidade de apoio diário uma preparação mais aprofundada por parte das pode estender-se por toda a vida. cuidadoras ou dos cuidadores informais. | 61 ANIGÁP | SIAMROFNI SERODADIUC SOD ODADIUCOTUA ERBOS RALAF SOMAV AS CUIDADORAS OU CUIDADORES INFORMAIS DE UMA CRIANÇA COM DEFICIÊNCIA PODEM SENTIR: Dificuldade em aceitar a situação. O confronto com o diagnóstico de deficiência de uma criança pode gerar choque, descrença no que está a acontecer, revolta, zanga quer com o profissional de saúde que nos deu a notícia, com o nosso parceiro ou parceira a ou até connosco. Por vezes, podemos sentir que ignoramos a criança e oscilar entre sentimentos de indiferença, rejeição e culpa. Estes sentimentos são comuns, difíceis de gerir e podem afetar a nossa relação com a criança. Por isso, é importante procurar apoio – um Psicólogo ou Psicóloga pode ajudar. Necessidade de fazer o luto por uma criança que se imaginou. É natural que, antes e durante a gravidez, os pais e mães desejem uma criança saudável e que até a imaginem com determinadas características. Quando percebemos que a criança é diferente daquilo que imaginámos, é comum sentirmo-nos tristes, impotentes, envergonhados, envergonhadas e, ou desiludidos, desiludidas. É importante permitir-nos sentir essas emoções e aprender a adaptar-nos a uma “criança real” que é diferente daquela que imaginámos, valorizando as suas particularidades e o seu potencial. Ansiedade e preocupação com o futuro da criança. É natural questionarmo-nos sobre se a criança poderá ter uma vida autónoma e feliz, fazer algo de que goste e manter relações significativas. Podemos ainda ter receio de que, se algo nos acontecer, a criança perca as pessoas que melhor a conhecem e mais a ajudam, ficando sem apoio. Stresse e dificuldades noutras áreas da vida. Com as aprendizagens e tarefas que se associam ao cuidar de uma criança com deficiência, podemos sentir-nos stressados e irritáveis, podendo ficar menos produtivas no trabalho ou investir menos na relação com o nosso parceiro ou parceira, outros filhos ou filhas, familiares e amigos ou amigas. Frustração com a falta de conhecimento sobre a deficiência. Além da exigência dos cuidados, podemos ter de lidar com pessoas que fazem comentários desadequados ou limitam a sua interação com a criança, em função de crenças desadequadas e falta de informação sobre a deficiência. Por exemplo, na escola, certos profissionais podem não saber lidar com as características da criança e adotar comportamentos que não ajudam a criança ou que dificultam a sua aprendizagem e inclusão. Estas situações podem levar-nos a sentir que estamos sozinhos/as ou em constante confronto com os outros – como o sentimento de que “somos nós contra o mundo”. Por outro lado, enquanto pessoa cuidadora de crianças com deficiência também podemos descobrir forças que não sabíamos que tínhamos. Com o passar do tempo e e com a experiência, podemos sentir mais confiança na nossa capacidade de lidar com situações desafiantes. Podemos olhar para as outras pessoascom mais sensibilidade e compaixão e até descobrir potencialidades onde outras pessoas não as veem. Cuidar de uma criança com deficiência também inclui momentos felizes. Assistir ao seu desenvolvimento - seja quando aprende a comunicar, conquista autonomia numa tarefa, desenvolve os seus interesses ou partilha momentos de brincadeira com os seus amigos), pode gerar sentimentos de orgulhoso, gratidão e esperança.\",\"Às vezes, podemos também sentir que o nosso parceiro ou a nossa parceira nos deixa com a maior parte das responsabilidade e tarefas de cuidado. Podemos acabar por nos sentir sozinhos ou sozinhas, atarefados ou atarefadas e sem tempo, priorizando sempre a responsabilidade de cuidar da pessoa. | 72 ANIGÁP | SIAMROFNI SERODADIUC SOD ODADIUCOTUA ERBOS RALAF SOMAV Algumas barreiras ao autocuidado podem ser ultrapassadas. Outras, podem ser difíceis de ultrapassar, porque não dependem apenas de nós. No entanto, há algumas soluções que podemos tentar: • Explorar a possibilidade de obter apoios sociais. Existem alguns apoios sociais que são destinados a cuidadores e cuidadoras informais e a pessoas que se encontram em situação de dependência. O Estatuto do Cuidador Informal concede alguns apoios, não só financeiros, mas também no acesso a uma maior rede de apoio. Também existem apoios da Segurança Social que se destinam a pessoas cuidadas. • Ir além de uma atitude paternalista e sobreprotetora. Por vezes, tendemos a ver a pessoa cuidada como alguém que quer que tomemos decisões por ela. No entanto, por muitas que possam ser as suas limitações, a pessoa terá alguma autonomia e capacidade para tomar decisões sobre si e a sua vida. Podemos questionar-nos se estaremos a proteger a pessoa em demasia, quando a pessoa cuidada até quereria tentar ou até consegue fazer algumas tarefas por si. • Comunicar com a pessoa cuidada sobre necessidades e soluções. Mesmo que existam dificuldades de compreensão (por exemplo, em casos de AVC ou demência), existe a possibilidade de explicar as nossas necessidades. Podemos, através de um diálogo calmo e que não desvalorize as necessidades da pessoa, falar sobre como é importante cuidarmos de nós, tentando encontrar soluções em conjunto. • Promover a autonomia e competências da pessoa cuidada. Quanto maior a autonomia da pessoa cuidada, maior será a nossa. Podemos desafiar a pessoa a tentar fazer tarefas por si, valorizando e elogiando as suas capacidades e conquistas. Por vezes, conquistar ou manter alguma autonomia é suficiente para termos mais algum tempo para nós. Devemos ajudar progressivamente na promoção desta autonomia, avaliando o risco de desafiar a pessoa a fazer certas tarefas. | 82 ANIGÁP | SIAMROFNI SERODADIUC SOD ODADIUCOTUA ERBOS RALAF SOMAV • Desafiar o que pensamos sobre ser cuidador ou cuidadora. Às vezes acreditamos que para cuidar bem temos de colocar todas as nossas necessidades de lado, ou que não há ninguém que possa cuidar tão bem como nós ou ainda que nos possa/queira ajudar. Mas, eventualmente, ao pensar assim estaremos a negligenciar oportunidades de obter ajuda. Um psicólogo ou psicóloga pode ajudar a alterar a nossa perceção sobre o próprio papel da pessoa cuidadora. • Criar uma rede de apoio com diferentes pessoas. Pedir e aceitar ajuda não é um sinal de fraqueza – é uma forma de autocuidado. Através de uma rede com familiares, amigos, amigas, vizinhos, vizinhas, voluntários e, inclusive, Assistentes Pessoais, é possível dividir responsabilidades e, assim, obter mais tempo para cuidar de nós. Será útil definir horários/responsabilidades para as diferentes pessoas (por exemplo, deixar o/a neto/a com a avó às quartas-feiras à tarde, enquanto vamos caminhar; o/a Assistente Pessoal garantir apoio semanal na parte da manhã; contar com a vizinha em saídas inesperadas, etc.). • Participar em ações de ativismo e reivindicação de direitos. Participar em grupos de apoio e associações, envolvendo-nos em campanhas de sensibilização junto de autoridades competentes, pode trazer maior visibilidade às nossas condições de vida e necessidades. Estas ações podem resultar em políticas que beneficiem todos os cuidadores e todas as cuidadoras e pessoas cuidadas – garantindo o direito ao descanso, maiores apoios financeiros, o suporte de voluntários e voluntárias de substituição temporária ou, ainda, o acesso a adaptações e profissionais qualificados e qualificadas.\",\"O AVC é uma como adaptações a novas rotinas de alimentação, das principais causas de incapacidade em Portugal higiene e mobilidade, sobretudo quanto maior for e pode deixar limitações funcionais, que incluem a a dificuldade da pessoa cuidada em realizar essas paralisação ou a dificuldade em movimentar partes tarefas de modo independente. O papel da cuidadodo corpo, a dificuldade em falar, ler ou escrever e ra ou do cuidador informal envolve não só o apoio a dificuldade em coordenar movimentos, impossi- prático e emocional no processo de adaptação, mas bilitando a realização autónoma de tarefas como também a gestão emocional associada à perda de agarrar nos talheres ou tomar banho. capacidades e a motivação para continuar a reabilitação. | 91 ANIGÁP | SIAMROFNI SERODADIUC SOD ODADIUCOTUA ERBOS RALAF SOMAV AS CUIDADORAS OU CUIDADORES INFORMAIS PODEM SENTIR: Que não sabem cuidar ou não são bons cuidadores, cuidadoras.. Cuidar de uma pessoa que sofreu um AVC é uma responsabilidade que surge de forma súbita e inesperada. Por isso, as cuidadoras ou os cuidadores são confrontados com tarefas que exigem conhecimentos técnicos e adaptações imediatas, sem qualquer formação prévia. No início, a cuidadora ou o cuidador precisa de aprender sobre as sequelas do AVC e os seus impactos, sobre as alterações necessárias a realizar na alimentação, sobre como gerir a medicação, a mobilização e os exercícios de reabilitação. Este processo de aprendizagem pode ser desgastante e fazer-nos sentir incompetentes – não porque sejamos maus cuidadores ou cuidadoras, mas porque se trata de um desafio novo, exigente e para o qual ninguém está, à partida, preparado, preaparada.. Frustração, devido a dificuldades na comunicação. Quando as capacidades de linguagem estão comprometidas, tentamos falar mais alto e/ou mais lentamente, repetimos várias vezes, escrevemos ou utilizamos gestos e imagens para tentar comunicar. Todas estas adaptações exigem um esforço consciente que, por vezes, quando as dificuldades persistem, nos podem deixar frustados, frustradas e desanimados ou desanimadas. Que a relação está desequilibrada. O que antes era uma relação mútua amorosa ou de amizade, pode passar a parecer-nos uma relação em que damos mais do que recebemos. Podemos ter esta sensação de desequilíbrio quando as limitações da pessoa são permanentes e graves e/ou quando nos é difícil aproveitar outras relações que são importantes para nós. Que a pessoa cuidada desconsidera a nossa perspetiva e os nossos esforços. Às vezes, podemos sentir-nos irritados, irritadas ou magoados, magoadas quando, apesar dos nossos esforços, a pessoa cuidada não entende e/ou não segue as recomendações dos profissionais de Saúde. Também pode tomar decisões que podem complicar o seu estado de Saúde (por exemplo, fumar, ignorar a dieta ou desistir dos exercícios de reabilitação). Que as dificuldades financeiras se tornam (mais) um problema. Isto é especialmente comum quando o/a sobrevivente é o/a nosso/a cônjuge, pois o que antes eram despesas suportadas pelos rendimentos de ambos/as passa agora a ser suportado apenas por uma pessoa, ao mesmo tempo que surgem despesas adicionais relacionadas com cuidados de Saúde. Que estamos “presos” ao papel de cuidador ou cuidadora. Em certos momentos, sobretudo quando a pessoa cuidada precisa de apoio para várias tarefas e parecem não existir progressos, podemos sentir que perdemos a nossa autonomia e independência e até parte da nossa identidade, ficando “presos” no papel de cuidadora ou cuidador permanentemente – algo que sinaliza a importância de encontrarmos soluções para descansarmos e partilharmos as nossas responsabilidades enquanto cuidador ou cuidadora Por outro lado, cuidadoras ou cuidadores informais de pessoas sobreviventes de um AVC também podem sentir orgulho da força e dos progressos da pessoa cuidada.\"]"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
     </font>
@@ -313,11 +319,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="3">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -331,66 +343,90 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -398,7 +434,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -588,24 +624,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:W37"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.13"/>
-    <col customWidth="1" min="2" max="2" width="8.13"/>
-    <col customWidth="1" min="3" max="3" width="58.38"/>
-    <col customWidth="1" min="4" max="4" width="41.63"/>
-    <col customWidth="1" min="5" max="5" width="37.13"/>
+    <col min="1" max="1" width="7.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.109375" customWidth="1"/>
+    <col min="3" max="3" width="58.33203125" style="15" customWidth="1"/>
+    <col min="4" max="4" width="41.6640625" customWidth="1"/>
+    <col min="5" max="5" width="72" style="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
+    <row r="1" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -618,7 +657,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -646,20 +685,20 @@
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>
     </row>
-    <row r="2" ht="15.0" customHeight="1">
+    <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="C2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="18" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="3"/>
@@ -681,21 +720,21 @@
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
     </row>
-    <row r="3" ht="15.0" customHeight="1">
+    <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>15</v>
+      <c r="E3" s="18" t="s">
+        <v>66</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -716,21 +755,21 @@
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
     </row>
-    <row r="4" ht="15.0" customHeight="1">
+    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="19" t="s">
         <v>18</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -751,21 +790,21 @@
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
     </row>
-    <row r="5" ht="15.0" customHeight="1">
+    <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>19</v>
+      <c r="E5" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -786,21 +825,21 @@
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
     </row>
-    <row r="6" ht="15.0" customHeight="1">
+    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="18" t="s">
         <v>25</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -821,21 +860,21 @@
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
     </row>
-    <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="6">
+        <v>2</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>30</v>
+      <c r="E7" s="20" t="s">
+        <v>67</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -856,21 +895,21 @@
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
     </row>
-    <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="6">
+        <v>2</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>34</v>
+      <c r="E8" s="20" t="s">
+        <v>69</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -891,21 +930,21 @@
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
     </row>
-    <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>19</v>
+    <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="6">
+        <v>2</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -926,21 +965,21 @@
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
     </row>
-    <row r="10" ht="15.0" customHeight="1">
+    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B10" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>39</v>
+        <v>3</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -961,21 +1000,21 @@
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
     </row>
-    <row r="11" ht="15.0" customHeight="1">
+    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B11" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>42</v>
+        <v>3</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>19</v>
+        <v>40</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -996,21 +1035,21 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
     </row>
-    <row r="12" ht="15.0" customHeight="1">
+    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B12" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>45</v>
+        <v>3</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>68</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -1031,25 +1070,25 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
     </row>
-    <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+    <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="8">
+        <v>3</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -1066,155 +1105,155 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17">
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="s">
+      <c r="C17" s="16"/>
+    </row>
+    <row r="18" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="16"/>
+    </row>
+    <row r="19" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="16"/>
+    </row>
+    <row r="20" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="16"/>
+    </row>
+    <row r="21" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="16"/>
+    </row>
+    <row r="22" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="16"/>
+    </row>
+    <row r="23" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24">
+      <c r="C23" s="16"/>
+    </row>
+    <row r="24" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="s">
+      <c r="C24" s="16"/>
+    </row>
+    <row r="25" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="16"/>
+    </row>
+    <row r="26" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="16"/>
+    </row>
+    <row r="27" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="16"/>
+    </row>
+    <row r="28" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="16"/>
+    </row>
+    <row r="29" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="16"/>
+    </row>
+    <row r="30" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31">
+      <c r="C30" s="16"/>
+    </row>
+    <row r="31" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="s">
+      <c r="C31" s="16"/>
+    </row>
+    <row r="32" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="16"/>
+    </row>
+    <row r="33" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="16"/>
+    </row>
+    <row r="34" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="16"/>
+    </row>
+    <row r="35" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="16"/>
+    </row>
+    <row r="36" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="16"/>
+    </row>
+    <row r="37" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
+      <c r="C37" s="16"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Avaliacao_Humano_Juiz.xlsx
+++ b/Avaliacao_Humano_Juiz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arliene\Downloads\avaliacao\avaliacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C9F552-A922-4688-9ACC-2A7A0423B550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3972A1-FF5D-4FB2-969A-5B5FAE2BEB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -358,7 +358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -387,13 +387,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -639,9 +637,9 @@
   <cols>
     <col min="1" max="1" width="7.109375" customWidth="1"/>
     <col min="2" max="2" width="8.109375" customWidth="1"/>
-    <col min="3" max="3" width="58.33203125" style="15" customWidth="1"/>
-    <col min="4" max="4" width="41.6640625" customWidth="1"/>
-    <col min="5" max="5" width="72" style="22" customWidth="1"/>
+    <col min="3" max="3" width="58.33203125" customWidth="1"/>
+    <col min="4" max="4" width="45.77734375" customWidth="1"/>
+    <col min="5" max="5" width="72" style="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -657,7 +655,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -698,7 +696,7 @@
       <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="16" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="3"/>
@@ -733,7 +731,7 @@
       <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="16" t="s">
         <v>66</v>
       </c>
       <c r="F3" s="3"/>
@@ -768,7 +766,7 @@
       <c r="D4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="17" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="3"/>
@@ -803,7 +801,7 @@
       <c r="D5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="17" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="3"/>
@@ -838,7 +836,7 @@
       <c r="D6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>25</v>
       </c>
       <c r="F6" s="3"/>
@@ -873,7 +871,7 @@
       <c r="D7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="18" t="s">
         <v>67</v>
       </c>
       <c r="F7" s="3"/>
@@ -908,7 +906,7 @@
       <c r="D8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="18" t="s">
         <v>69</v>
       </c>
       <c r="F8" s="3"/>
@@ -943,7 +941,7 @@
       <c r="D9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="17" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="3"/>
@@ -978,7 +976,7 @@
       <c r="D10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="17" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="3"/>
@@ -1013,7 +1011,7 @@
       <c r="D11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="17" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="3"/>
@@ -1048,7 +1046,7 @@
       <c r="D12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="16" t="s">
         <v>68</v>
       </c>
       <c r="F12" s="3"/>
@@ -1083,7 +1081,7 @@
       <c r="D13" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="19" t="s">
         <v>66</v>
       </c>
       <c r="F13" s="10"/>
@@ -1110,148 +1108,148 @@
         <v>47</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="16"/>
+      <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="16"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>48</v>
       </c>
       <c r="B18" s="3"/>
-      <c r="C18" s="16"/>
+      <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="16"/>
+      <c r="C19" s="3"/>
     </row>
     <row r="20" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B20" s="3"/>
-      <c r="C20" s="16"/>
+      <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B21" s="3"/>
-      <c r="C21" s="16"/>
+      <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B22" s="3"/>
-      <c r="C22" s="16"/>
+      <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B23" s="3"/>
-      <c r="C23" s="16"/>
+      <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
-      <c r="C24" s="16"/>
+      <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>54</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="16"/>
+      <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="16"/>
+      <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B27" s="3"/>
-      <c r="C27" s="16"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B28" s="3"/>
-      <c r="C28" s="16"/>
+      <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B29" s="3"/>
-      <c r="C29" s="16"/>
+      <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B30" s="3"/>
-      <c r="C30" s="16"/>
+      <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
-      <c r="C31" s="16"/>
+      <c r="C31" s="3"/>
     </row>
     <row r="32" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>60</v>
       </c>
       <c r="B32" s="3"/>
-      <c r="C32" s="16"/>
+      <c r="C32" s="3"/>
     </row>
     <row r="33" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B33" s="3"/>
-      <c r="C33" s="16"/>
+      <c r="C33" s="3"/>
     </row>
     <row r="34" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B34" s="3"/>
-      <c r="C34" s="16"/>
+      <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B35" s="3"/>
-      <c r="C35" s="16"/>
+      <c r="C35" s="3"/>
     </row>
     <row r="36" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B36" s="3"/>
-      <c r="C36" s="16"/>
+      <c r="C36" s="3"/>
     </row>
     <row r="37" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B37" s="3"/>
-      <c r="C37" s="16"/>
+      <c r="C37" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
